--- a/research/traditional_assets/database/data/bangladesh/bangladesh_tobacco.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1108585436146709</v>
+        <v>0.1105574679838269</v>
       </c>
       <c r="C2">
-        <v>1694.746620534345</v>
+        <v>1682.303401992464</v>
       </c>
       <c r="D2">
-        <v>1607.546620534345</v>
+        <v>1612.012401992464</v>
       </c>
       <c r="E2">
-        <v>-33.2</v>
+        <v>-16.291</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>16.909</v>
       </c>
       <c r="G2">
         <v>87.2</v>
@@ -1451,28 +1451,28 @@
         <v>288.91</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8505227000000001</v>
       </c>
       <c r="N2">
-        <v>288.91</v>
+        <v>288.0594773</v>
       </c>
       <c r="O2">
-        <v>86.673</v>
+        <v>86.41784319</v>
       </c>
       <c r="P2">
-        <v>202.237</v>
+        <v>201.64163411</v>
       </c>
       <c r="Q2">
-        <v>205.827</v>
+        <v>205.23163411</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1108585436146709</v>
+        <v>0.1113185535190171</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5612177595389388</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>339.685231211348</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1105574679838269</v>
+        <v>0.1102563923529829</v>
       </c>
       <c r="C3">
-        <v>1682.303401992464</v>
+        <v>1669.885064546466</v>
       </c>
       <c r="D3">
-        <v>1612.012401992464</v>
+        <v>1616.503064546466</v>
       </c>
       <c r="E3">
-        <v>-16.291</v>
+        <v>0.6180000000000021</v>
       </c>
       <c r="F3">
-        <v>16.909</v>
+        <v>33.818</v>
       </c>
       <c r="G3">
         <v>87.2</v>
@@ -1533,28 +1533,28 @@
         <v>288.91</v>
       </c>
       <c r="M3">
-        <v>0.8505227000000001</v>
+        <v>1.7010454</v>
       </c>
       <c r="N3">
-        <v>288.0594773</v>
+        <v>287.2089546</v>
       </c>
       <c r="O3">
-        <v>86.41784319</v>
+        <v>86.16268638000001</v>
       </c>
       <c r="P3">
-        <v>201.64163411</v>
+        <v>201.04626822</v>
       </c>
       <c r="Q3">
-        <v>205.23163411</v>
+        <v>204.63626822</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1113185535190171</v>
+        <v>0.1117879513805948</v>
       </c>
       <c r="T3">
-        <v>0.5612177595389388</v>
+        <v>0.5652385201030521</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>339.685231211348</v>
+        <v>169.842615605674</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1102563923529829</v>
+        <v>0.1099553167221389</v>
       </c>
       <c r="C4">
-        <v>1669.885064546466</v>
+        <v>1657.491816714722</v>
       </c>
       <c r="D4">
-        <v>1616.503064546466</v>
+        <v>1621.018816714722</v>
       </c>
       <c r="E4">
-        <v>0.6180000000000021</v>
+        <v>17.527</v>
       </c>
       <c r="F4">
-        <v>33.818</v>
+        <v>50.727</v>
       </c>
       <c r="G4">
         <v>87.2</v>
@@ -1615,28 +1615,28 @@
         <v>288.91</v>
       </c>
       <c r="M4">
-        <v>1.7010454</v>
+        <v>2.5515681</v>
       </c>
       <c r="N4">
-        <v>287.2089546</v>
+        <v>286.3584319</v>
       </c>
       <c r="O4">
-        <v>86.16268638000001</v>
+        <v>85.90752957000001</v>
       </c>
       <c r="P4">
-        <v>201.04626822</v>
+        <v>200.45090233</v>
       </c>
       <c r="Q4">
-        <v>204.63626822</v>
+        <v>204.04090233</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1117879513805948</v>
+        <v>0.1122670275485968</v>
       </c>
       <c r="T4">
-        <v>0.5652385201030521</v>
+        <v>0.5693421829468379</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>169.842615605674</v>
+        <v>113.2284104037827</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1099553167221389</v>
+        <v>0.1096542410912948</v>
       </c>
       <c r="C5">
-        <v>1657.491816714722</v>
+        <v>1645.123869352142</v>
       </c>
       <c r="D5">
-        <v>1621.018816714722</v>
+        <v>1625.559869352142</v>
       </c>
       <c r="E5">
-        <v>17.527</v>
+        <v>34.43600000000001</v>
       </c>
       <c r="F5">
-        <v>50.727</v>
+        <v>67.63600000000001</v>
       </c>
       <c r="G5">
         <v>87.2</v>
@@ -1697,28 +1697,28 @@
         <v>288.91</v>
       </c>
       <c r="M5">
-        <v>2.5515681</v>
+        <v>3.4020908</v>
       </c>
       <c r="N5">
-        <v>286.3584319</v>
+        <v>285.5079092</v>
       </c>
       <c r="O5">
-        <v>85.90752957000001</v>
+        <v>85.65237276000001</v>
       </c>
       <c r="P5">
-        <v>200.45090233</v>
+        <v>199.85553644</v>
       </c>
       <c r="Q5">
-        <v>204.04090233</v>
+        <v>203.44553644</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1122670275485968</v>
+        <v>0.1127560844700988</v>
       </c>
       <c r="T5">
-        <v>0.5693421829468379</v>
+        <v>0.5735313387665358</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>113.2284104037827</v>
+        <v>84.92130780283701</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1096542410912948</v>
+        <v>0.1093531654604508</v>
       </c>
       <c r="C6">
-        <v>1645.123869352142</v>
+        <v>1632.781435682994</v>
       </c>
       <c r="D6">
-        <v>1625.559869352142</v>
+        <v>1630.126435682994</v>
       </c>
       <c r="E6">
-        <v>34.43600000000001</v>
+        <v>51.34500000000001</v>
       </c>
       <c r="F6">
-        <v>67.63600000000001</v>
+        <v>84.54500000000002</v>
       </c>
       <c r="G6">
         <v>87.2</v>
@@ -1779,28 +1779,28 @@
         <v>288.91</v>
       </c>
       <c r="M6">
-        <v>3.4020908</v>
+        <v>4.252613500000001</v>
       </c>
       <c r="N6">
-        <v>285.5079092</v>
+        <v>284.6573865</v>
       </c>
       <c r="O6">
-        <v>85.65237276000001</v>
+        <v>85.39721595</v>
       </c>
       <c r="P6">
-        <v>199.85553644</v>
+        <v>199.26017055</v>
       </c>
       <c r="Q6">
-        <v>203.44553644</v>
+        <v>202.85017055</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1127560844700988</v>
+        <v>0.1132554373267904</v>
       </c>
       <c r="T6">
-        <v>0.5735313387665358</v>
+        <v>0.5778086873403327</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>84.92130780283701</v>
+        <v>67.9370462422696</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1093531654604508</v>
+        <v>0.1090520898296068</v>
       </c>
       <c r="C7">
-        <v>1632.781435682994</v>
+        <v>1620.464731334276</v>
       </c>
       <c r="D7">
-        <v>1630.126435682994</v>
+        <v>1634.718731334276</v>
       </c>
       <c r="E7">
-        <v>51.34500000000001</v>
+        <v>68.254</v>
       </c>
       <c r="F7">
-        <v>84.54500000000002</v>
+        <v>101.454</v>
       </c>
       <c r="G7">
         <v>87.2</v>
@@ -1861,28 +1861,28 @@
         <v>288.91</v>
       </c>
       <c r="M7">
-        <v>4.252613500000001</v>
+        <v>5.1031362</v>
       </c>
       <c r="N7">
-        <v>284.6573865</v>
+        <v>283.8068638</v>
       </c>
       <c r="O7">
-        <v>85.39721595</v>
+        <v>85.14205914</v>
       </c>
       <c r="P7">
-        <v>199.26017055</v>
+        <v>198.66480466</v>
       </c>
       <c r="Q7">
-        <v>202.85017055</v>
+        <v>202.25480466</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1132554373267904</v>
+        <v>0.1137654147123477</v>
       </c>
       <c r="T7">
-        <v>0.5778086873403327</v>
+        <v>0.5821770433305934</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>67.9370462422696</v>
+        <v>56.61420520189134</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1090520898296068</v>
+        <v>0.1087510141987628</v>
       </c>
       <c r="C8">
-        <v>1620.464731334276</v>
+        <v>1608.173974369657</v>
       </c>
       <c r="D8">
-        <v>1634.718731334276</v>
+        <v>1639.336974369657</v>
       </c>
       <c r="E8">
-        <v>68.254</v>
+        <v>85.163</v>
       </c>
       <c r="F8">
-        <v>101.454</v>
+        <v>118.363</v>
       </c>
       <c r="G8">
         <v>87.2</v>
@@ -1943,28 +1943,28 @@
         <v>288.91</v>
       </c>
       <c r="M8">
-        <v>5.1031362</v>
+        <v>5.9536589</v>
       </c>
       <c r="N8">
-        <v>283.8068638</v>
+        <v>282.9563411</v>
       </c>
       <c r="O8">
-        <v>85.14205914</v>
+        <v>84.88690233000001</v>
       </c>
       <c r="P8">
-        <v>198.66480466</v>
+        <v>198.06943877</v>
       </c>
       <c r="Q8">
-        <v>202.25480466</v>
+        <v>201.65943877</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1137654147123477</v>
+        <v>0.1142863593535084</v>
       </c>
       <c r="T8">
-        <v>0.5821770433305934</v>
+        <v>0.5866393424604296</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.61420520189134</v>
+        <v>48.52646160162116</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1087510141987628</v>
+        <v>0.1084499385679188</v>
       </c>
       <c r="C9">
-        <v>1608.173974369657</v>
+        <v>1595.909385323993</v>
       </c>
       <c r="D9">
-        <v>1639.336974369657</v>
+        <v>1643.981385323993</v>
       </c>
       <c r="E9">
-        <v>85.16300000000001</v>
+        <v>102.072</v>
       </c>
       <c r="F9">
-        <v>118.363</v>
+        <v>135.272</v>
       </c>
       <c r="G9">
         <v>87.2</v>
@@ -2025,28 +2025,28 @@
         <v>288.91</v>
       </c>
       <c r="M9">
-        <v>5.953658900000001</v>
+        <v>6.804181600000001</v>
       </c>
       <c r="N9">
-        <v>282.9563411</v>
+        <v>282.1058184</v>
       </c>
       <c r="O9">
-        <v>84.88690233000001</v>
+        <v>84.63174552000001</v>
       </c>
       <c r="P9">
-        <v>198.06943877</v>
+        <v>197.47407288</v>
       </c>
       <c r="Q9">
-        <v>201.65943877</v>
+        <v>201.06407288</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1142863593535084</v>
+        <v>0.1148186288781726</v>
       </c>
       <c r="T9">
-        <v>0.5866393424604296</v>
+        <v>0.5911986480930883</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.52646160162115</v>
+        <v>42.4606539014185</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1084499385679188</v>
+        <v>0.1081488629370748</v>
       </c>
       <c r="C10">
-        <v>1595.909385323993</v>
+        <v>1583.671187238435</v>
       </c>
       <c r="D10">
-        <v>1643.981385323993</v>
+        <v>1648.652187238435</v>
       </c>
       <c r="E10">
-        <v>102.072</v>
+        <v>118.981</v>
       </c>
       <c r="F10">
-        <v>135.272</v>
+        <v>152.181</v>
       </c>
       <c r="G10">
         <v>87.2</v>
@@ -2107,28 +2107,28 @@
         <v>288.91</v>
       </c>
       <c r="M10">
-        <v>6.804181600000001</v>
+        <v>7.654704300000001</v>
       </c>
       <c r="N10">
-        <v>282.1058184</v>
+        <v>281.2552957</v>
       </c>
       <c r="O10">
-        <v>84.63174552000001</v>
+        <v>84.37658871000001</v>
       </c>
       <c r="P10">
-        <v>197.47407288</v>
+        <v>196.87870699</v>
       </c>
       <c r="Q10">
-        <v>201.06407288</v>
+        <v>200.46870699</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1148186288781726</v>
+        <v>0.1153625966341481</v>
       </c>
       <c r="T10">
-        <v>0.5911986480930883</v>
+        <v>0.595858158245146</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.4606539014185</v>
+        <v>37.74280346792756</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1081488629370748</v>
+        <v>0.1078477873062308</v>
       </c>
       <c r="C11">
-        <v>1583.671187238435</v>
+        <v>1571.45960569613</v>
       </c>
       <c r="D11">
-        <v>1648.652187238435</v>
+        <v>1653.34960569613</v>
       </c>
       <c r="E11">
-        <v>118.981</v>
+        <v>135.89</v>
       </c>
       <c r="F11">
-        <v>152.181</v>
+        <v>169.09</v>
       </c>
       <c r="G11">
         <v>87.2</v>
@@ -2189,28 +2189,28 @@
         <v>288.91</v>
       </c>
       <c r="M11">
-        <v>7.654704300000001</v>
+        <v>8.505227</v>
       </c>
       <c r="N11">
-        <v>281.2552957</v>
+        <v>280.404773</v>
       </c>
       <c r="O11">
-        <v>84.37658871000001</v>
+        <v>84.1214319</v>
       </c>
       <c r="P11">
-        <v>196.87870699</v>
+        <v>196.2833411</v>
       </c>
       <c r="Q11">
-        <v>200.46870699</v>
+        <v>199.8733411</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1153625966341481</v>
+        <v>0.1159186525624786</v>
       </c>
       <c r="T11">
-        <v>0.595858158245146</v>
+        <v>0.6006212130672495</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.74280346792756</v>
+        <v>33.96852312113481</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1078477873062308</v>
+        <v>0.1075467116753868</v>
       </c>
       <c r="C12">
-        <v>1571.45960569613</v>
+        <v>1559.27486885854</v>
       </c>
       <c r="D12">
-        <v>1653.34960569613</v>
+        <v>1658.07386885854</v>
       </c>
       <c r="E12">
-        <v>135.89</v>
+        <v>152.799</v>
       </c>
       <c r="F12">
-        <v>169.09</v>
+        <v>185.999</v>
       </c>
       <c r="G12">
         <v>87.2</v>
@@ -2271,28 +2271,28 @@
         <v>288.91</v>
       </c>
       <c r="M12">
-        <v>8.505227000000001</v>
+        <v>9.355749700000001</v>
       </c>
       <c r="N12">
-        <v>280.404773</v>
+        <v>279.5542503</v>
       </c>
       <c r="O12">
-        <v>84.1214319</v>
+        <v>83.86627509</v>
       </c>
       <c r="P12">
-        <v>196.2833411</v>
+        <v>195.68797521</v>
       </c>
       <c r="Q12">
-        <v>199.8733411</v>
+        <v>199.2779752100001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1159186525624786</v>
+        <v>0.1164872041296481</v>
       </c>
       <c r="T12">
-        <v>0.6006212130672495</v>
+        <v>0.6054913028291755</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>33.9685231211348</v>
+        <v>30.880475564668</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1075467116753868</v>
+        <v>0.1072456360445427</v>
       </c>
       <c r="C13">
-        <v>1559.27486885854</v>
+        <v>1547.117207502385</v>
       </c>
       <c r="D13">
-        <v>1658.07386885854</v>
+        <v>1662.825207502385</v>
       </c>
       <c r="E13">
-        <v>152.799</v>
+        <v>169.708</v>
       </c>
       <c r="F13">
-        <v>185.999</v>
+        <v>202.908</v>
       </c>
       <c r="G13">
         <v>87.2</v>
@@ -2353,28 +2353,28 @@
         <v>288.91</v>
       </c>
       <c r="M13">
-        <v>9.355749700000001</v>
+        <v>10.2062724</v>
       </c>
       <c r="N13">
-        <v>279.5542503</v>
+        <v>278.7037276</v>
       </c>
       <c r="O13">
-        <v>83.86627509</v>
+        <v>83.61111828000001</v>
       </c>
       <c r="P13">
-        <v>195.68797521</v>
+        <v>195.09260932</v>
       </c>
       <c r="Q13">
-        <v>199.2779752100001</v>
+        <v>198.68260932</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1164872041296481</v>
+        <v>0.117068677323344</v>
       </c>
       <c r="T13">
-        <v>0.6054913028291755</v>
+        <v>0.6104720764493271</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>30.880475564668</v>
+        <v>28.30710260094568</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1072456360445427</v>
+        <v>0.1069445604136987</v>
       </c>
       <c r="C14">
-        <v>1547.117207502385</v>
+        <v>1534.986855057221</v>
       </c>
       <c r="D14">
-        <v>1662.825207502385</v>
+        <v>1667.603855057221</v>
       </c>
       <c r="E14">
-        <v>169.708</v>
+        <v>186.617</v>
       </c>
       <c r="F14">
-        <v>202.908</v>
+        <v>219.817</v>
       </c>
       <c r="G14">
         <v>87.2</v>
@@ -2435,28 +2435,28 @@
         <v>288.91</v>
       </c>
       <c r="M14">
-        <v>10.2062724</v>
+        <v>11.0567951</v>
       </c>
       <c r="N14">
-        <v>278.7037276</v>
+        <v>277.8532049</v>
       </c>
       <c r="O14">
-        <v>83.61111828000001</v>
+        <v>83.35596147000001</v>
       </c>
       <c r="P14">
-        <v>195.09260932</v>
+        <v>194.49724343</v>
       </c>
       <c r="Q14">
-        <v>198.68260932</v>
+        <v>198.08724343</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.117068677323344</v>
+        <v>0.1176635177168951</v>
       </c>
       <c r="T14">
-        <v>0.6104720764493271</v>
+        <v>0.6155673506124707</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.30710260094568</v>
+        <v>26.1296331701037</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1069445604136987</v>
+        <v>0.1066434847828547</v>
       </c>
       <c r="C15">
-        <v>1534.986855057221</v>
+        <v>1522.884047643669</v>
       </c>
       <c r="D15">
-        <v>1667.603855057221</v>
+        <v>1672.410047643669</v>
       </c>
       <c r="E15">
-        <v>186.617</v>
+        <v>203.526</v>
       </c>
       <c r="F15">
-        <v>219.817</v>
+        <v>236.726</v>
       </c>
       <c r="G15">
         <v>87.2</v>
@@ -2517,28 +2517,28 @@
         <v>288.91</v>
       </c>
       <c r="M15">
-        <v>11.0567951</v>
+        <v>11.9073178</v>
       </c>
       <c r="N15">
-        <v>277.8532049</v>
+        <v>277.0026822</v>
       </c>
       <c r="O15">
-        <v>83.35596147000001</v>
+        <v>83.10080466000001</v>
       </c>
       <c r="P15">
-        <v>194.49724343</v>
+        <v>193.90187754</v>
       </c>
       <c r="Q15">
-        <v>198.08724343</v>
+        <v>197.49187754</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1176635177168951</v>
+        <v>0.1182721916079706</v>
       </c>
       <c r="T15">
-        <v>0.6155673506124707</v>
+        <v>0.6207811195235944</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.1296331701037</v>
+        <v>24.26323080081058</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1066434847828547</v>
+        <v>0.1063424091520107</v>
       </c>
       <c r="C16">
-        <v>1522.884047643669</v>
+        <v>1510.809024112304</v>
       </c>
       <c r="D16">
-        <v>1672.410047643669</v>
+        <v>1677.244024112304</v>
       </c>
       <c r="E16">
-        <v>203.526</v>
+        <v>220.4350000000001</v>
       </c>
       <c r="F16">
-        <v>236.726</v>
+        <v>253.635</v>
       </c>
       <c r="G16">
         <v>87.2</v>
@@ -2599,28 +2599,28 @@
         <v>288.91</v>
       </c>
       <c r="M16">
-        <v>11.9073178</v>
+        <v>12.7578405</v>
       </c>
       <c r="N16">
-        <v>277.0026822</v>
+        <v>276.1521595</v>
       </c>
       <c r="O16">
-        <v>83.10080466000001</v>
+        <v>82.84564785000001</v>
       </c>
       <c r="P16">
-        <v>193.90187754</v>
+        <v>193.30651165</v>
       </c>
       <c r="Q16">
-        <v>197.49187754</v>
+        <v>196.89651165</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1182721916079706</v>
+        <v>0.1188951872376597</v>
       </c>
       <c r="T16">
-        <v>0.6207811195235944</v>
+        <v>0.6261175653502741</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.26323080081058</v>
+        <v>22.64568208075654</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1063424091520107</v>
+        <v>0.1060413335211667</v>
       </c>
       <c r="C17">
-        <v>1510.809024112304</v>
+        <v>1498.762026083227</v>
       </c>
       <c r="D17">
-        <v>1677.244024112304</v>
+        <v>1682.106026083227</v>
       </c>
       <c r="E17">
-        <v>220.435</v>
+        <v>237.3440000000001</v>
       </c>
       <c r="F17">
-        <v>253.635</v>
+        <v>270.544</v>
       </c>
       <c r="G17">
         <v>87.2</v>
@@ -2681,28 +2681,28 @@
         <v>288.91</v>
       </c>
       <c r="M17">
-        <v>12.7578405</v>
+        <v>13.6083632</v>
       </c>
       <c r="N17">
-        <v>276.1521595</v>
+        <v>275.3016368</v>
       </c>
       <c r="O17">
-        <v>82.84564785000001</v>
+        <v>82.59049104</v>
       </c>
       <c r="P17">
-        <v>193.30651165</v>
+        <v>192.71114576</v>
       </c>
       <c r="Q17">
-        <v>196.89651165</v>
+        <v>196.30114576</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1188951872376597</v>
+        <v>0.119533016096627</v>
       </c>
       <c r="T17">
-        <v>0.6261175653502741</v>
+        <v>0.6315810694109221</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.64568208075654</v>
+        <v>21.23032695070925</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1060413335211667</v>
+        <v>0.1057402578903227</v>
       </c>
       <c r="C18">
-        <v>1498.762026083227</v>
+        <v>1486.743297986322</v>
       </c>
       <c r="D18">
-        <v>1682.106026083227</v>
+        <v>1686.996297986322</v>
       </c>
       <c r="E18">
-        <v>237.3440000000001</v>
+        <v>254.253</v>
       </c>
       <c r="F18">
-        <v>270.544</v>
+        <v>287.453</v>
       </c>
       <c r="G18">
         <v>87.2</v>
@@ -2763,28 +2763,28 @@
         <v>288.91</v>
       </c>
       <c r="M18">
-        <v>13.6083632</v>
+        <v>14.4588859</v>
       </c>
       <c r="N18">
-        <v>275.3016368</v>
+        <v>274.4511141</v>
       </c>
       <c r="O18">
-        <v>82.59049104</v>
+        <v>82.33533423000002</v>
       </c>
       <c r="P18">
-        <v>192.71114576</v>
+        <v>192.11577987</v>
       </c>
       <c r="Q18">
-        <v>196.30114576</v>
+        <v>195.70577987</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.119533016096627</v>
+        <v>0.12018621432569</v>
       </c>
       <c r="T18">
-        <v>0.6315810694109221</v>
+        <v>0.6371762241718268</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.23032695070925</v>
+        <v>19.98148418890283</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1057402578903227</v>
+        <v>0.1054391822594787</v>
       </c>
       <c r="C19">
-        <v>1486.743297986322</v>
+        <v>1474.753087102216</v>
       </c>
       <c r="D19">
-        <v>1686.996297986322</v>
+        <v>1691.915087102216</v>
       </c>
       <c r="E19">
-        <v>254.253</v>
+        <v>271.1620000000001</v>
       </c>
       <c r="F19">
-        <v>287.453</v>
+        <v>304.3620000000001</v>
       </c>
       <c r="G19">
         <v>87.2</v>
@@ -2845,28 +2845,28 @@
         <v>288.91</v>
       </c>
       <c r="M19">
-        <v>14.4588859</v>
+        <v>15.3094086</v>
       </c>
       <c r="N19">
-        <v>274.4511141</v>
+        <v>273.6005914</v>
       </c>
       <c r="O19">
-        <v>82.33533423000002</v>
+        <v>82.08017742000001</v>
       </c>
       <c r="P19">
-        <v>192.11577987</v>
+        <v>191.52041398</v>
       </c>
       <c r="Q19">
-        <v>195.70577987</v>
+        <v>195.11041398</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.12018621432569</v>
+        <v>0.1208553442188764</v>
       </c>
       <c r="T19">
-        <v>0.6371762241718268</v>
+        <v>0.6429078461220218</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.98148418890283</v>
+        <v>18.87140173396378</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1054391822594787</v>
+        <v>0.1051381066286347</v>
       </c>
       <c r="C20">
-        <v>1474.753087102216</v>
+        <v>1462.791643603964</v>
       </c>
       <c r="D20">
-        <v>1691.915087102216</v>
+        <v>1696.862643603964</v>
       </c>
       <c r="E20">
-        <v>271.162</v>
+        <v>288.071</v>
       </c>
       <c r="F20">
-        <v>304.362</v>
+        <v>321.271</v>
       </c>
       <c r="G20">
         <v>87.2</v>
@@ -2927,28 +2927,28 @@
         <v>288.91</v>
       </c>
       <c r="M20">
-        <v>15.3094086</v>
+        <v>16.1599313</v>
       </c>
       <c r="N20">
-        <v>273.6005914</v>
+        <v>272.7500687</v>
       </c>
       <c r="O20">
-        <v>82.08017742000001</v>
+        <v>81.82502061000001</v>
       </c>
       <c r="P20">
-        <v>191.52041398</v>
+        <v>190.92504809</v>
       </c>
       <c r="Q20">
-        <v>195.11041398</v>
+        <v>194.51504809</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1208553442188764</v>
+        <v>0.1215409958378206</v>
       </c>
       <c r="T20">
-        <v>0.6429078461220218</v>
+        <v>0.6487809896018514</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.87140173396378</v>
+        <v>17.87817006375516</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1051381066286347</v>
+        <v>0.1048370309977907</v>
       </c>
       <c r="C21">
-        <v>1462.791643603964</v>
+        <v>1450.85922059946</v>
       </c>
       <c r="D21">
-        <v>1696.862643603964</v>
+        <v>1701.83922059946</v>
       </c>
       <c r="E21">
-        <v>288.071</v>
+        <v>304.9800000000001</v>
       </c>
       <c r="F21">
-        <v>321.271</v>
+        <v>338.1800000000001</v>
       </c>
       <c r="G21">
         <v>87.2</v>
@@ -3009,28 +3009,28 @@
         <v>288.91</v>
       </c>
       <c r="M21">
-        <v>16.1599313</v>
+        <v>17.010454</v>
       </c>
       <c r="N21">
-        <v>272.7500687</v>
+        <v>271.899546</v>
       </c>
       <c r="O21">
-        <v>81.82502061000001</v>
+        <v>81.56986380000001</v>
       </c>
       <c r="P21">
-        <v>190.92504809</v>
+        <v>190.3296822</v>
       </c>
       <c r="Q21">
-        <v>194.51504809</v>
+        <v>193.9196822</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1215409958378206</v>
+        <v>0.1222437887472383</v>
       </c>
       <c r="T21">
-        <v>0.6487809896018514</v>
+        <v>0.6548009616686766</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.87817006375516</v>
+        <v>16.9842615605674</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1048370309977907</v>
+        <v>0.1045359553669466</v>
       </c>
       <c r="C22">
-        <v>1450.85922059946</v>
+        <v>1438.956074174604</v>
       </c>
       <c r="D22">
-        <v>1701.83922059946</v>
+        <v>1706.845074174604</v>
       </c>
       <c r="E22">
-        <v>304.9800000000001</v>
+        <v>321.8890000000001</v>
       </c>
       <c r="F22">
-        <v>338.1800000000001</v>
+        <v>355.0890000000001</v>
       </c>
       <c r="G22">
         <v>87.2</v>
@@ -3091,28 +3091,28 @@
         <v>288.91</v>
       </c>
       <c r="M22">
-        <v>17.010454</v>
+        <v>17.8609767</v>
       </c>
       <c r="N22">
-        <v>271.899546</v>
+        <v>271.0490233</v>
       </c>
       <c r="O22">
-        <v>81.56986380000001</v>
+        <v>81.31470699</v>
       </c>
       <c r="P22">
-        <v>190.3296822</v>
+        <v>189.7343163100001</v>
       </c>
       <c r="Q22">
-        <v>193.9196822</v>
+        <v>193.3243163100001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1222437887472383</v>
+        <v>0.1229643738822109</v>
       </c>
       <c r="T22">
-        <v>0.6548009616686766</v>
+        <v>0.6609733380916241</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.9842615605674</v>
+        <v>16.17548720054038</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1045359553669466</v>
+        <v>0.1042348797361026</v>
       </c>
       <c r="C23">
-        <v>1438.956074174604</v>
+        <v>1427.082463437227</v>
       </c>
       <c r="D23">
-        <v>1706.845074174604</v>
+        <v>1711.880463437227</v>
       </c>
       <c r="E23">
-        <v>321.889</v>
+        <v>338.7980000000001</v>
       </c>
       <c r="F23">
-        <v>355.089</v>
+        <v>371.998</v>
       </c>
       <c r="G23">
         <v>87.2</v>
@@ -3173,28 +3173,28 @@
         <v>288.91</v>
       </c>
       <c r="M23">
-        <v>17.8609767</v>
+        <v>18.7114994</v>
       </c>
       <c r="N23">
-        <v>271.0490233</v>
+        <v>270.1985006</v>
       </c>
       <c r="O23">
-        <v>81.31470699</v>
+        <v>81.05955018000002</v>
       </c>
       <c r="P23">
-        <v>189.7343163100001</v>
+        <v>189.13895042</v>
       </c>
       <c r="Q23">
-        <v>193.3243163100001</v>
+        <v>192.72895042</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1229643738822109</v>
+        <v>0.1237034355591059</v>
       </c>
       <c r="T23">
-        <v>0.660973338091624</v>
+        <v>0.6673039805766983</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.17548720054039</v>
+        <v>15.440237782334</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1042348797361026</v>
+        <v>0.1039338041052586</v>
       </c>
       <c r="C24">
-        <v>1427.082463437227</v>
+        <v>1415.238650561798</v>
       </c>
       <c r="D24">
-        <v>1711.880463437227</v>
+        <v>1716.945650561798</v>
       </c>
       <c r="E24">
-        <v>338.7980000000001</v>
+        <v>355.7070000000001</v>
       </c>
       <c r="F24">
-        <v>371.998</v>
+        <v>388.907</v>
       </c>
       <c r="G24">
         <v>87.2</v>
@@ -3255,28 +3255,28 @@
         <v>288.91</v>
       </c>
       <c r="M24">
-        <v>18.7114994</v>
+        <v>19.5620221</v>
       </c>
       <c r="N24">
-        <v>270.1985006</v>
+        <v>269.3479779</v>
       </c>
       <c r="O24">
-        <v>81.05955018000002</v>
+        <v>80.80439337000001</v>
       </c>
       <c r="P24">
-        <v>189.13895042</v>
+        <v>188.54358453</v>
       </c>
       <c r="Q24">
-        <v>192.72895042</v>
+        <v>192.13358453</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1237034355591059</v>
+        <v>0.124461693643193</v>
       </c>
       <c r="T24">
-        <v>0.6673039805766983</v>
+        <v>0.6737990553341121</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.440237782334</v>
+        <v>14.76892309614557</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1039338041052586</v>
+        <v>0.1036327284744146</v>
       </c>
       <c r="C25">
-        <v>1415.238650561798</v>
+        <v>1403.424900834927</v>
       </c>
       <c r="D25">
-        <v>1716.945650561798</v>
+        <v>1722.040900834927</v>
       </c>
       <c r="E25">
-        <v>355.7070000000001</v>
+        <v>372.616</v>
       </c>
       <c r="F25">
-        <v>388.907</v>
+        <v>405.816</v>
       </c>
       <c r="G25">
         <v>87.2</v>
@@ -3337,28 +3337,28 @@
         <v>288.91</v>
       </c>
       <c r="M25">
-        <v>19.5620221</v>
+        <v>20.4125448</v>
       </c>
       <c r="N25">
-        <v>269.3479779</v>
+        <v>268.4974552</v>
       </c>
       <c r="O25">
-        <v>80.80439337000001</v>
+        <v>80.54923656000001</v>
       </c>
       <c r="P25">
-        <v>188.54358453</v>
+        <v>187.9482186400001</v>
       </c>
       <c r="Q25">
-        <v>192.13358453</v>
+        <v>191.5382186400001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.124461693643193</v>
+        <v>0.1252399058873876</v>
       </c>
       <c r="T25">
-        <v>0.6737990553341121</v>
+        <v>0.6804650531114579</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.76892309614557</v>
+        <v>14.15355130047284</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1036327284744146</v>
+        <v>0.1033316528435706</v>
       </c>
       <c r="C26">
-        <v>1403.424900834927</v>
+        <v>1391.641482701682</v>
       </c>
       <c r="D26">
-        <v>1722.040900834927</v>
+        <v>1727.166482701683</v>
       </c>
       <c r="E26">
-        <v>372.616</v>
+        <v>389.525</v>
       </c>
       <c r="F26">
-        <v>405.816</v>
+        <v>422.725</v>
       </c>
       <c r="G26">
         <v>87.2</v>
@@ -3419,28 +3419,28 @@
         <v>288.91</v>
       </c>
       <c r="M26">
-        <v>20.4125448</v>
+        <v>21.2630675</v>
       </c>
       <c r="N26">
-        <v>268.4974552</v>
+        <v>267.6469325</v>
       </c>
       <c r="O26">
-        <v>80.54923656000001</v>
+        <v>80.29407975000001</v>
       </c>
       <c r="P26">
-        <v>187.9482186400001</v>
+        <v>187.35285275</v>
       </c>
       <c r="Q26">
-        <v>191.5382186400001</v>
+        <v>190.94285275</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1252399058873876</v>
+        <v>0.1260388704580941</v>
       </c>
       <c r="T26">
-        <v>0.6804650531114579</v>
+        <v>0.687308810829533</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.15355130047284</v>
+        <v>13.58740924845392</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1033316528435706</v>
+        <v>0.1030305772127266</v>
       </c>
       <c r="C27">
-        <v>1391.641482701682</v>
+        <v>1379.888667812737</v>
       </c>
       <c r="D27">
-        <v>1727.166482701683</v>
+        <v>1732.322667812737</v>
       </c>
       <c r="E27">
-        <v>389.525</v>
+        <v>406.434</v>
       </c>
       <c r="F27">
-        <v>422.725</v>
+        <v>439.634</v>
       </c>
       <c r="G27">
         <v>87.2</v>
@@ -3501,28 +3501,28 @@
         <v>288.91</v>
       </c>
       <c r="M27">
-        <v>21.2630675</v>
+        <v>22.1135902</v>
       </c>
       <c r="N27">
-        <v>267.6469325</v>
+        <v>266.7964098</v>
       </c>
       <c r="O27">
-        <v>80.29407975000001</v>
+        <v>80.03892294000001</v>
       </c>
       <c r="P27">
-        <v>187.35285275</v>
+        <v>186.75748686</v>
       </c>
       <c r="Q27">
-        <v>190.94285275</v>
+        <v>190.34748686</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1260388704580941</v>
+        <v>0.1268594286658467</v>
       </c>
       <c r="T27">
-        <v>0.687308810829533</v>
+        <v>0.6943375349724207</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.58740924845392</v>
+        <v>13.06481658505185</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1030305772127266</v>
+        <v>0.1030130015818826</v>
       </c>
       <c r="C28">
-        <v>1379.888667812737</v>
+        <v>1363.281617161086</v>
       </c>
       <c r="D28">
-        <v>1732.322667812737</v>
+        <v>1732.624617161086</v>
       </c>
       <c r="E28">
-        <v>406.434</v>
+        <v>423.3430000000001</v>
       </c>
       <c r="F28">
-        <v>439.634</v>
+        <v>456.5430000000001</v>
       </c>
       <c r="G28">
         <v>87.2</v>
@@ -3583,45 +3583,45 @@
         <v>288.91</v>
       </c>
       <c r="M28">
-        <v>22.1135902</v>
+        <v>23.6489274</v>
       </c>
       <c r="N28">
-        <v>266.7964098</v>
+        <v>265.2610726</v>
       </c>
       <c r="O28">
-        <v>80.03892294000001</v>
+        <v>79.57832178000001</v>
       </c>
       <c r="P28">
-        <v>186.75748686</v>
+        <v>185.68275082</v>
       </c>
       <c r="Q28">
-        <v>190.34748686</v>
+        <v>189.27275082</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1268594286658467</v>
+        <v>0.1277024679203871</v>
       </c>
       <c r="T28">
-        <v>0.6943375349724207</v>
+        <v>0.7015588269000453</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.06481658505185</v>
+        <v>12.21662171452224</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1030130015818826</v>
+        <v>0.1027224259510385</v>
       </c>
       <c r="C29">
-        <v>1363.281617161086</v>
+        <v>1351.38000676322</v>
       </c>
       <c r="D29">
-        <v>1732.624617161086</v>
+        <v>1737.63200676322</v>
       </c>
       <c r="E29">
-        <v>423.3430000000001</v>
+        <v>440.2520000000001</v>
       </c>
       <c r="F29">
-        <v>456.5430000000001</v>
+        <v>473.4520000000001</v>
       </c>
       <c r="G29">
         <v>87.2</v>
@@ -3665,28 +3665,28 @@
         <v>288.91</v>
       </c>
       <c r="M29">
-        <v>23.6489274</v>
+        <v>24.5248136</v>
       </c>
       <c r="N29">
-        <v>265.2610726</v>
+        <v>264.3851864</v>
       </c>
       <c r="O29">
-        <v>79.57832178000001</v>
+        <v>79.31555591999999</v>
       </c>
       <c r="P29">
-        <v>185.68275082</v>
+        <v>185.06963048</v>
       </c>
       <c r="Q29">
-        <v>189.27275082</v>
+        <v>188.65963048</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1277024679203871</v>
+        <v>0.128568924931998</v>
       </c>
       <c r="T29">
-        <v>0.7015588269000453</v>
+        <v>0.7089807102701037</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.21662171452224</v>
+        <v>11.78031379614645</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1027224259510385</v>
+        <v>0.1024318503201945</v>
       </c>
       <c r="C30">
-        <v>1351.38000676322</v>
+        <v>1339.507423571413</v>
       </c>
       <c r="D30">
-        <v>1737.63200676322</v>
+        <v>1742.668423571413</v>
       </c>
       <c r="E30">
-        <v>440.2520000000001</v>
+        <v>457.1610000000001</v>
       </c>
       <c r="F30">
-        <v>473.4520000000001</v>
+        <v>490.3610000000001</v>
       </c>
       <c r="G30">
         <v>87.2</v>
@@ -3747,28 +3747,28 @@
         <v>288.91</v>
       </c>
       <c r="M30">
-        <v>24.5248136</v>
+        <v>25.40069980000001</v>
       </c>
       <c r="N30">
-        <v>264.3851864</v>
+        <v>263.5093002</v>
       </c>
       <c r="O30">
-        <v>79.31555591999999</v>
+        <v>79.05279006000001</v>
       </c>
       <c r="P30">
-        <v>185.06963048</v>
+        <v>184.45651014</v>
       </c>
       <c r="Q30">
-        <v>188.65963048</v>
+        <v>188.04651014</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.128568924931998</v>
+        <v>0.1294597891833726</v>
       </c>
       <c r="T30">
-        <v>0.7089807102701037</v>
+        <v>0.7166116607773471</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.78031379614645</v>
+        <v>11.37409607903795</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1024318503201945</v>
+        <v>0.1021412746893505</v>
       </c>
       <c r="C31">
-        <v>1339.507423571413</v>
+        <v>1327.664120719938</v>
       </c>
       <c r="D31">
-        <v>1742.668423571413</v>
+        <v>1747.734120719937</v>
       </c>
       <c r="E31">
-        <v>457.161</v>
+        <v>474.07</v>
       </c>
       <c r="F31">
-        <v>490.361</v>
+        <v>507.27</v>
       </c>
       <c r="G31">
         <v>87.2</v>
@@ -3829,28 +3829,28 @@
         <v>288.91</v>
       </c>
       <c r="M31">
-        <v>25.4006998</v>
+        <v>26.276586</v>
       </c>
       <c r="N31">
-        <v>263.5093002</v>
+        <v>262.633414</v>
       </c>
       <c r="O31">
-        <v>79.05279006000001</v>
+        <v>78.7900242</v>
       </c>
       <c r="P31">
-        <v>184.45651014</v>
+        <v>183.8433898</v>
       </c>
       <c r="Q31">
-        <v>188.04651014</v>
+        <v>187.4333898</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1294597891833726</v>
+        <v>0.1303761066990722</v>
       </c>
       <c r="T31">
-        <v>0.7166116607773471</v>
+        <v>0.7244606384419401</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.37409607903795</v>
+        <v>10.99495954307002</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1021412746893505</v>
+        <v>0.1018506990585065</v>
       </c>
       <c r="C32">
-        <v>1327.664120719938</v>
+        <v>1315.850354294954</v>
       </c>
       <c r="D32">
-        <v>1747.734120719937</v>
+        <v>1752.829354294954</v>
       </c>
       <c r="E32">
-        <v>474.07</v>
+        <v>490.979</v>
       </c>
       <c r="F32">
-        <v>507.27</v>
+        <v>524.179</v>
       </c>
       <c r="G32">
         <v>87.2</v>
@@ -3911,28 +3911,28 @@
         <v>288.91</v>
       </c>
       <c r="M32">
-        <v>26.276586</v>
+        <v>27.1524722</v>
       </c>
       <c r="N32">
-        <v>262.633414</v>
+        <v>261.7575278</v>
       </c>
       <c r="O32">
-        <v>78.7900242</v>
+        <v>78.52725834000002</v>
       </c>
       <c r="P32">
-        <v>183.8433898</v>
+        <v>183.23026946</v>
       </c>
       <c r="Q32">
-        <v>187.4333898</v>
+        <v>186.82026946</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1303761066990722</v>
+        <v>0.1313189841427631</v>
       </c>
       <c r="T32">
-        <v>0.7244606384419401</v>
+        <v>0.7325371227055069</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.99495954307002</v>
+        <v>10.64028342877744</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1018506990585065</v>
+        <v>0.1015601234276625</v>
       </c>
       <c r="C33">
-        <v>1315.850354294954</v>
+        <v>1304.066383377664</v>
       </c>
       <c r="D33">
-        <v>1752.829354294954</v>
+        <v>1757.954383377664</v>
       </c>
       <c r="E33">
-        <v>490.979</v>
+        <v>507.8880000000001</v>
       </c>
       <c r="F33">
-        <v>524.179</v>
+        <v>541.0880000000001</v>
       </c>
       <c r="G33">
         <v>87.2</v>
@@ -3993,28 +3993,28 @@
         <v>288.91</v>
       </c>
       <c r="M33">
-        <v>27.1524722</v>
+        <v>28.0283584</v>
       </c>
       <c r="N33">
-        <v>261.7575278</v>
+        <v>260.8816416</v>
       </c>
       <c r="O33">
-        <v>78.52725834000002</v>
+        <v>78.26449248</v>
       </c>
       <c r="P33">
-        <v>183.23026946</v>
+        <v>182.61714912</v>
       </c>
       <c r="Q33">
-        <v>186.82026946</v>
+        <v>186.20714912</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1313189841427631</v>
+        <v>0.1322895932759743</v>
       </c>
       <c r="T33">
-        <v>0.7325371227055069</v>
+        <v>0.7408511506238844</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.64028342877744</v>
+        <v>10.30777457162814</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1015601234276625</v>
+        <v>0.1012695477968185</v>
       </c>
       <c r="C34">
-        <v>1304.066383377664</v>
+        <v>1292.312470088223</v>
       </c>
       <c r="D34">
-        <v>1757.954383377664</v>
+        <v>1763.109470088223</v>
       </c>
       <c r="E34">
-        <v>507.8880000000001</v>
+        <v>524.797</v>
       </c>
       <c r="F34">
-        <v>541.0880000000001</v>
+        <v>557.9970000000001</v>
       </c>
       <c r="G34">
         <v>87.2</v>
@@ -4075,28 +4075,28 @@
         <v>288.91</v>
       </c>
       <c r="M34">
-        <v>28.0283584</v>
+        <v>28.9042446</v>
       </c>
       <c r="N34">
-        <v>260.8816416</v>
+        <v>260.0057554</v>
       </c>
       <c r="O34">
-        <v>78.26449248</v>
+        <v>78.00172662</v>
       </c>
       <c r="P34">
-        <v>182.61714912</v>
+        <v>182.00402878</v>
       </c>
       <c r="Q34">
-        <v>186.20714912</v>
+        <v>185.59402878</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1322895932759743</v>
+        <v>0.133289175816147</v>
       </c>
       <c r="T34">
-        <v>0.7408511506238844</v>
+        <v>0.7494133584801241</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.30777457162814</v>
+        <v>9.995417766427288</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1012695477968185</v>
+        <v>0.1013835721659744</v>
       </c>
       <c r="C35">
-        <v>1292.312470088223</v>
+        <v>1273.376969755719</v>
       </c>
       <c r="D35">
-        <v>1763.109470088223</v>
+        <v>1761.082969755719</v>
       </c>
       <c r="E35">
-        <v>524.797</v>
+        <v>541.706</v>
       </c>
       <c r="F35">
-        <v>557.9970000000001</v>
+        <v>574.9060000000001</v>
       </c>
       <c r="G35">
         <v>87.2</v>
@@ -4157,45 +4157,45 @@
         <v>288.91</v>
       </c>
       <c r="M35">
-        <v>28.9042446</v>
+        <v>30.757471</v>
       </c>
       <c r="N35">
-        <v>260.0057554</v>
+        <v>258.152529</v>
       </c>
       <c r="O35">
-        <v>78.00172662</v>
+        <v>77.4457587</v>
       </c>
       <c r="P35">
-        <v>182.00402878</v>
+        <v>180.7067703</v>
       </c>
       <c r="Q35">
-        <v>185.59402878</v>
+        <v>184.2967703</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.133289175816147</v>
+        <v>0.1343190487363249</v>
       </c>
       <c r="T35">
-        <v>0.7494133584801241</v>
+        <v>0.7582350271804921</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>9.995417766427288</v>
+        <v>9.393164997213198</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1013835721659744</v>
+        <v>0.1011048965351304</v>
       </c>
       <c r="C36">
-        <v>1273.376969755719</v>
+        <v>1261.428981223127</v>
       </c>
       <c r="D36">
-        <v>1761.082969755719</v>
+        <v>1766.043981223127</v>
       </c>
       <c r="E36">
-        <v>541.706</v>
+        <v>558.615</v>
       </c>
       <c r="F36">
-        <v>574.9060000000001</v>
+        <v>591.8150000000001</v>
       </c>
       <c r="G36">
         <v>87.2</v>
@@ -4239,28 +4239,28 @@
         <v>288.91</v>
       </c>
       <c r="M36">
-        <v>30.757471</v>
+        <v>31.6621025</v>
       </c>
       <c r="N36">
-        <v>258.152529</v>
+        <v>257.2478975</v>
       </c>
       <c r="O36">
-        <v>77.4457587</v>
+        <v>77.17436925</v>
       </c>
       <c r="P36">
-        <v>180.7067703</v>
+        <v>180.07352825</v>
       </c>
       <c r="Q36">
-        <v>184.2967703</v>
+        <v>183.66352825</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1343190487363249</v>
+        <v>0.1353806100540469</v>
       </c>
       <c r="T36">
-        <v>0.7582350271804921</v>
+        <v>0.7673281318408715</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.393164997213198</v>
+        <v>9.124788854435677</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1011048965351304</v>
+        <v>0.1008262209042864</v>
       </c>
       <c r="C37">
-        <v>1261.428981223127</v>
+        <v>1249.509022218511</v>
       </c>
       <c r="D37">
-        <v>1766.043981223127</v>
+        <v>1771.033022218511</v>
       </c>
       <c r="E37">
-        <v>558.615</v>
+        <v>575.5240000000001</v>
       </c>
       <c r="F37">
-        <v>591.8150000000001</v>
+        <v>608.7240000000002</v>
       </c>
       <c r="G37">
         <v>87.2</v>
@@ -4321,28 +4321,28 @@
         <v>288.91</v>
       </c>
       <c r="M37">
-        <v>31.6621025</v>
+        <v>32.56673400000001</v>
       </c>
       <c r="N37">
-        <v>257.2478975</v>
+        <v>256.343266</v>
       </c>
       <c r="O37">
-        <v>77.17436925</v>
+        <v>76.90297980000001</v>
       </c>
       <c r="P37">
-        <v>180.07352825</v>
+        <v>179.4402862</v>
       </c>
       <c r="Q37">
-        <v>183.66352825</v>
+        <v>183.0302862</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1353806100540469</v>
+        <v>0.1364753451629476</v>
       </c>
       <c r="T37">
-        <v>0.7673281318408715</v>
+        <v>0.7767053960218877</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.124788854435677</v>
+        <v>8.871322497368018</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1008262209042864</v>
+        <v>0.1005475452734424</v>
       </c>
       <c r="C38">
-        <v>1249.509022218511</v>
+        <v>1237.61733096351</v>
       </c>
       <c r="D38">
-        <v>1771.033022218511</v>
+        <v>1776.05033096351</v>
       </c>
       <c r="E38">
-        <v>575.524</v>
+        <v>592.433</v>
       </c>
       <c r="F38">
-        <v>608.724</v>
+        <v>625.633</v>
       </c>
       <c r="G38">
         <v>87.2</v>
@@ -4403,28 +4403,28 @@
         <v>288.91</v>
       </c>
       <c r="M38">
-        <v>32.566734</v>
+        <v>33.4713655</v>
       </c>
       <c r="N38">
-        <v>256.343266</v>
+        <v>255.4386345</v>
       </c>
       <c r="O38">
-        <v>76.90297980000001</v>
+        <v>76.63159035000001</v>
       </c>
       <c r="P38">
-        <v>179.4402862</v>
+        <v>178.80704415</v>
       </c>
       <c r="Q38">
-        <v>183.0302862</v>
+        <v>182.39704415</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1364753451629476</v>
+        <v>0.1376048337673689</v>
       </c>
       <c r="T38">
-        <v>0.7767053960218877</v>
+        <v>0.7863803511292853</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.87132249736802</v>
+        <v>8.631557024466181</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1005475452734424</v>
+        <v>0.1002688696425984</v>
       </c>
       <c r="C39">
-        <v>1237.61733096351</v>
+        <v>1225.754148386943</v>
       </c>
       <c r="D39">
-        <v>1776.05033096351</v>
+        <v>1781.096148386943</v>
       </c>
       <c r="E39">
-        <v>592.433</v>
+        <v>609.342</v>
       </c>
       <c r="F39">
-        <v>625.633</v>
+        <v>642.542</v>
       </c>
       <c r="G39">
         <v>87.2</v>
@@ -4485,28 +4485,28 @@
         <v>288.91</v>
       </c>
       <c r="M39">
-        <v>33.4713655</v>
+        <v>34.375997</v>
       </c>
       <c r="N39">
-        <v>255.4386345</v>
+        <v>254.534003</v>
       </c>
       <c r="O39">
-        <v>76.63159035000001</v>
+        <v>76.36020090000001</v>
       </c>
       <c r="P39">
-        <v>178.80704415</v>
+        <v>178.1738021</v>
       </c>
       <c r="Q39">
-        <v>182.39704415</v>
+        <v>181.7638021</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1376048337673689</v>
+        <v>0.1387707574880619</v>
       </c>
       <c r="T39">
-        <v>0.7863803511292853</v>
+        <v>0.7963674015627281</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.631557024466181</v>
+        <v>8.404410786980231</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1002688696425984</v>
+        <v>0.09999019401175439</v>
       </c>
       <c r="C40">
-        <v>1225.754148386943</v>
+        <v>1213.919718163378</v>
       </c>
       <c r="D40">
-        <v>1781.096148386943</v>
+        <v>1786.170718163378</v>
       </c>
       <c r="E40">
-        <v>609.342</v>
+        <v>626.251</v>
       </c>
       <c r="F40">
-        <v>642.542</v>
+        <v>659.451</v>
       </c>
       <c r="G40">
         <v>87.2</v>
@@ -4567,28 +4567,28 @@
         <v>288.91</v>
       </c>
       <c r="M40">
-        <v>34.375997</v>
+        <v>35.2806285</v>
       </c>
       <c r="N40">
-        <v>254.534003</v>
+        <v>253.6293715</v>
       </c>
       <c r="O40">
-        <v>76.36020090000001</v>
+        <v>76.08881145000001</v>
       </c>
       <c r="P40">
-        <v>178.1738021</v>
+        <v>177.54056005</v>
       </c>
       <c r="Q40">
-        <v>181.7638021</v>
+        <v>181.13056005</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1387707574880619</v>
+        <v>0.1399749082159908</v>
       </c>
       <c r="T40">
-        <v>0.7963674015627281</v>
+        <v>0.8066818962726773</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.404410786980231</v>
+        <v>8.188913074493557</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09999019401175439</v>
+        <v>0.09971151838091039</v>
       </c>
       <c r="C41">
-        <v>1213.919718163378</v>
+        <v>1202.114286752356</v>
       </c>
       <c r="D41">
-        <v>1786.170718163378</v>
+        <v>1791.274286752356</v>
       </c>
       <c r="E41">
-        <v>626.251</v>
+        <v>643.1600000000001</v>
       </c>
       <c r="F41">
-        <v>659.451</v>
+        <v>676.3600000000001</v>
       </c>
       <c r="G41">
         <v>87.2</v>
@@ -4649,28 +4649,28 @@
         <v>288.91</v>
       </c>
       <c r="M41">
-        <v>35.2806285</v>
+        <v>36.18526000000001</v>
       </c>
       <c r="N41">
-        <v>253.6293715</v>
+        <v>252.72474</v>
       </c>
       <c r="O41">
-        <v>76.08881145000001</v>
+        <v>75.81742200000001</v>
       </c>
       <c r="P41">
-        <v>177.54056005</v>
+        <v>176.907318</v>
       </c>
       <c r="Q41">
-        <v>181.13056005</v>
+        <v>180.497318</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1399749082159908</v>
+        <v>0.1412191973015173</v>
       </c>
       <c r="T41">
-        <v>0.8066818962726773</v>
+        <v>0.8173402074729581</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.188913074493557</v>
+        <v>7.984190247631218</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09971151838091039</v>
+        <v>0.09943284275006639</v>
       </c>
       <c r="C42">
-        <v>1202.114286752356</v>
+        <v>1190.338103438296</v>
       </c>
       <c r="D42">
-        <v>1791.274286752356</v>
+        <v>1796.407103438296</v>
       </c>
       <c r="E42">
-        <v>643.1600000000001</v>
+        <v>660.0690000000001</v>
       </c>
       <c r="F42">
-        <v>676.3600000000001</v>
+        <v>693.2690000000001</v>
       </c>
       <c r="G42">
         <v>87.2</v>
@@ -4731,28 +4731,28 @@
         <v>288.91</v>
       </c>
       <c r="M42">
-        <v>36.18526000000001</v>
+        <v>37.08989150000001</v>
       </c>
       <c r="N42">
-        <v>252.72474</v>
+        <v>251.8201085</v>
       </c>
       <c r="O42">
-        <v>75.81742200000001</v>
+        <v>75.54603254999999</v>
       </c>
       <c r="P42">
-        <v>176.907318</v>
+        <v>176.27407595</v>
       </c>
       <c r="Q42">
-        <v>180.497318</v>
+        <v>179.86407595</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1412191973015173</v>
+        <v>0.1425056656780786</v>
       </c>
       <c r="T42">
-        <v>0.8173402074729581</v>
+        <v>0.8283598173579941</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.984190247631218</v>
+        <v>7.789453900128017</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09943284275006639</v>
+        <v>0.09938936711922236</v>
       </c>
       <c r="C43">
-        <v>1190.338103438296</v>
+        <v>1174.23251765668</v>
       </c>
       <c r="D43">
-        <v>1796.407103438296</v>
+        <v>1797.21051765668</v>
       </c>
       <c r="E43">
-        <v>660.0690000000001</v>
+        <v>676.9780000000001</v>
       </c>
       <c r="F43">
-        <v>693.2690000000001</v>
+        <v>710.1780000000001</v>
       </c>
       <c r="G43">
         <v>87.2</v>
@@ -4813,45 +4813,45 @@
         <v>288.91</v>
       </c>
       <c r="M43">
-        <v>37.08989150000001</v>
+        <v>38.56266540000001</v>
       </c>
       <c r="N43">
-        <v>251.8201085</v>
+        <v>250.3473346</v>
       </c>
       <c r="O43">
-        <v>75.54603254999999</v>
+        <v>75.10420037999999</v>
       </c>
       <c r="P43">
-        <v>176.27407595</v>
+        <v>175.24313422</v>
       </c>
       <c r="Q43">
-        <v>179.86407595</v>
+        <v>178.83313422</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1425056656780786</v>
+        <v>0.143836495033142</v>
       </c>
       <c r="T43">
-        <v>0.8283598173579941</v>
+        <v>0.83975941379079</v>
       </c>
       <c r="U43">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>7.789453900128017</v>
+        <v>7.491961382939053</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09938936711922236</v>
+        <v>0.09911629148837836</v>
       </c>
       <c r="C44">
-        <v>1174.23251765668</v>
+        <v>1162.386337348958</v>
       </c>
       <c r="D44">
-        <v>1797.21051765668</v>
+        <v>1802.273337348958</v>
       </c>
       <c r="E44">
-        <v>676.978</v>
+        <v>693.8869999999999</v>
       </c>
       <c r="F44">
-        <v>710.178</v>
+        <v>727.087</v>
       </c>
       <c r="G44">
         <v>87.2</v>
@@ -4895,28 +4895,28 @@
         <v>288.91</v>
       </c>
       <c r="M44">
-        <v>38.5626654</v>
+        <v>39.4808241</v>
       </c>
       <c r="N44">
-        <v>250.3473346</v>
+        <v>249.4291759</v>
       </c>
       <c r="O44">
-        <v>75.10420037999999</v>
+        <v>74.82875277000001</v>
       </c>
       <c r="P44">
-        <v>175.24313422</v>
+        <v>174.60042313</v>
       </c>
       <c r="Q44">
-        <v>178.83313422</v>
+        <v>178.19042313</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.143836495033142</v>
+        <v>0.1452140201550498</v>
       </c>
       <c r="T44">
-        <v>0.8397594137907899</v>
+        <v>0.8515589960633331</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.491961382939054</v>
+        <v>7.317729722870705</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09911629148837836</v>
+        <v>0.09884321585753433</v>
       </c>
       <c r="C45">
-        <v>1162.386337348958</v>
+        <v>1150.568761986316</v>
       </c>
       <c r="D45">
-        <v>1802.273337348958</v>
+        <v>1807.364761986316</v>
       </c>
       <c r="E45">
-        <v>693.8869999999999</v>
+        <v>710.796</v>
       </c>
       <c r="F45">
-        <v>727.087</v>
+        <v>743.9960000000001</v>
       </c>
       <c r="G45">
         <v>87.2</v>
@@ -4977,28 +4977,28 @@
         <v>288.91</v>
       </c>
       <c r="M45">
-        <v>39.4808241</v>
+        <v>40.39898280000001</v>
       </c>
       <c r="N45">
-        <v>249.4291759</v>
+        <v>248.5110172</v>
       </c>
       <c r="O45">
-        <v>74.82875277000001</v>
+        <v>74.55330516000001</v>
       </c>
       <c r="P45">
-        <v>174.60042313</v>
+        <v>173.95771204</v>
       </c>
       <c r="Q45">
-        <v>178.19042313</v>
+        <v>177.54771204</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1452140201550498</v>
+        <v>0.1466407426027399</v>
       </c>
       <c r="T45">
-        <v>0.8515589960633331</v>
+        <v>0.8637799919884669</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.317729722870705</v>
+        <v>7.151417683714551</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09884321585753433</v>
+        <v>0.09857014022669033</v>
       </c>
       <c r="C46">
-        <v>1150.568761986316</v>
+        <v>1138.780034682575</v>
       </c>
       <c r="D46">
-        <v>1807.364761986316</v>
+        <v>1812.485034682575</v>
       </c>
       <c r="E46">
-        <v>710.796</v>
+        <v>727.705</v>
       </c>
       <c r="F46">
-        <v>743.9960000000001</v>
+        <v>760.9050000000001</v>
       </c>
       <c r="G46">
         <v>87.2</v>
@@ -5059,28 +5059,28 @@
         <v>288.91</v>
       </c>
       <c r="M46">
-        <v>40.39898280000001</v>
+        <v>41.31714150000001</v>
       </c>
       <c r="N46">
-        <v>248.5110172</v>
+        <v>247.5928585</v>
       </c>
       <c r="O46">
-        <v>74.55330516000001</v>
+        <v>74.27785755000001</v>
       </c>
       <c r="P46">
-        <v>173.95771204</v>
+        <v>173.31500095</v>
       </c>
       <c r="Q46">
-        <v>177.54771204</v>
+        <v>176.90500095</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1466407426027399</v>
+        <v>0.1481193458667097</v>
       </c>
       <c r="T46">
-        <v>0.8637799919884669</v>
+        <v>0.876445387765424</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.151417683714551</v>
+        <v>6.992497290743117</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09857014022669033</v>
+        <v>0.09829706459584631</v>
       </c>
       <c r="C47">
-        <v>1138.780034682575</v>
+        <v>1127.020401314357</v>
       </c>
       <c r="D47">
-        <v>1812.485034682575</v>
+        <v>1817.634401314357</v>
       </c>
       <c r="E47">
-        <v>727.705</v>
+        <v>744.614</v>
       </c>
       <c r="F47">
-        <v>760.9050000000001</v>
+        <v>777.8140000000001</v>
       </c>
       <c r="G47">
         <v>87.2</v>
@@ -5141,28 +5141,28 @@
         <v>288.91</v>
       </c>
       <c r="M47">
-        <v>41.31714150000001</v>
+        <v>42.2353002</v>
       </c>
       <c r="N47">
-        <v>247.5928585</v>
+        <v>246.6746998</v>
       </c>
       <c r="O47">
-        <v>74.27785755000001</v>
+        <v>74.00240994000001</v>
       </c>
       <c r="P47">
-        <v>173.31500095</v>
+        <v>172.67228986</v>
       </c>
       <c r="Q47">
-        <v>176.90500095</v>
+        <v>176.26228986</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1481193458667097</v>
+        <v>0.1496527122145302</v>
       </c>
       <c r="T47">
-        <v>0.876445387765424</v>
+        <v>0.8895798722748608</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.992497290743117</v>
+        <v>6.840486480074788</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09829706459584631</v>
+        <v>0.09802398896500229</v>
       </c>
       <c r="C48">
-        <v>1127.020401314357</v>
+        <v>1115.290110560439</v>
       </c>
       <c r="D48">
-        <v>1817.634401314357</v>
+        <v>1822.813110560439</v>
       </c>
       <c r="E48">
-        <v>744.614</v>
+        <v>761.523</v>
       </c>
       <c r="F48">
-        <v>777.8140000000001</v>
+        <v>794.7230000000001</v>
       </c>
       <c r="G48">
         <v>87.2</v>
@@ -5223,28 +5223,28 @@
         <v>288.91</v>
       </c>
       <c r="M48">
-        <v>42.2353002</v>
+        <v>43.1534589</v>
       </c>
       <c r="N48">
-        <v>246.6746998</v>
+        <v>245.7565411</v>
       </c>
       <c r="O48">
-        <v>74.00240994000001</v>
+        <v>73.72696233000001</v>
       </c>
       <c r="P48">
-        <v>172.67228986</v>
+        <v>172.02957877</v>
       </c>
       <c r="Q48">
-        <v>176.26228986</v>
+        <v>175.61957877</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1496527122145302</v>
+        <v>0.1512439414434006</v>
       </c>
       <c r="T48">
-        <v>0.8895798722748608</v>
+        <v>0.9032099977091822</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.840486480074788</v>
+        <v>6.694944214541282</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09802398896500229</v>
+        <v>0.09775091333415828</v>
       </c>
       <c r="C49">
-        <v>1115.290110560439</v>
+        <v>1103.589413941785</v>
       </c>
       <c r="D49">
-        <v>1822.813110560439</v>
+        <v>1828.021413941785</v>
       </c>
       <c r="E49">
-        <v>761.523</v>
+        <v>778.432</v>
       </c>
       <c r="F49">
-        <v>794.7230000000001</v>
+        <v>811.6320000000001</v>
       </c>
       <c r="G49">
         <v>87.2</v>
@@ -5305,28 +5305,28 @@
         <v>288.91</v>
       </c>
       <c r="M49">
-        <v>43.1534589</v>
+        <v>44.0716176</v>
       </c>
       <c r="N49">
-        <v>245.7565411</v>
+        <v>244.8383824</v>
       </c>
       <c r="O49">
-        <v>73.72696233000001</v>
+        <v>73.45151472000001</v>
       </c>
       <c r="P49">
-        <v>172.02957877</v>
+        <v>171.38686768</v>
       </c>
       <c r="Q49">
-        <v>175.61957877</v>
+        <v>174.97686768</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1512439414434006</v>
+        <v>0.1528963717964582</v>
       </c>
       <c r="T49">
-        <v>0.9032099977091822</v>
+        <v>0.9173643587371312</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.694944214541282</v>
+        <v>6.555466210071672</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09775091333415828</v>
+        <v>0.09747783770331427</v>
       </c>
       <c r="C50">
-        <v>1103.589413941785</v>
+        <v>1091.918565862268</v>
       </c>
       <c r="D50">
-        <v>1828.021413941785</v>
+        <v>1833.259565862268</v>
       </c>
       <c r="E50">
-        <v>778.432</v>
+        <v>795.341</v>
       </c>
       <c r="F50">
-        <v>811.6320000000001</v>
+        <v>828.5410000000001</v>
       </c>
       <c r="G50">
         <v>87.2</v>
@@ -5387,28 +5387,28 @@
         <v>288.91</v>
       </c>
       <c r="M50">
-        <v>44.0716176</v>
+        <v>44.9897763</v>
       </c>
       <c r="N50">
-        <v>244.8383824</v>
+        <v>243.9202237</v>
       </c>
       <c r="O50">
-        <v>73.45151472000001</v>
+        <v>73.17606711000001</v>
       </c>
       <c r="P50">
-        <v>171.38686768</v>
+        <v>170.74415659</v>
       </c>
       <c r="Q50">
-        <v>174.97686768</v>
+        <v>174.33415659</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1528963717964582</v>
+        <v>0.1546136033398319</v>
       </c>
       <c r="T50">
-        <v>0.9173643587371312</v>
+        <v>0.9320737927465684</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.555466210071672</v>
+        <v>6.421681185376332</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09747783770331427</v>
+        <v>0.09720476207247027</v>
       </c>
       <c r="C51">
-        <v>1091.918565862268</v>
+        <v>1080.277823650096</v>
       </c>
       <c r="D51">
-        <v>1833.259565862268</v>
+        <v>1838.527823650096</v>
       </c>
       <c r="E51">
-        <v>795.341</v>
+        <v>812.25</v>
       </c>
       <c r="F51">
-        <v>828.5410000000001</v>
+        <v>845.45</v>
       </c>
       <c r="G51">
         <v>87.2</v>
@@ -5469,28 +5469,28 @@
         <v>288.91</v>
       </c>
       <c r="M51">
-        <v>44.9897763</v>
+        <v>45.907935</v>
       </c>
       <c r="N51">
-        <v>243.9202237</v>
+        <v>243.002065</v>
       </c>
       <c r="O51">
-        <v>73.17606711000001</v>
+        <v>72.9006195</v>
       </c>
       <c r="P51">
-        <v>170.74415659</v>
+        <v>170.1014455</v>
       </c>
       <c r="Q51">
-        <v>174.33415659</v>
+        <v>173.6914455</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1546136033398319</v>
+        <v>0.1563995241449405</v>
       </c>
       <c r="T51">
-        <v>0.9320737927465684</v>
+        <v>0.9473716041163832</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.421681185376332</v>
+        <v>6.293247561668806</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09720476207247027</v>
+        <v>0.09693168644162627</v>
       </c>
       <c r="C52">
-        <v>1080.277823650096</v>
+        <v>1068.667447599947</v>
       </c>
       <c r="D52">
-        <v>1838.527823650096</v>
+        <v>1843.826447599947</v>
       </c>
       <c r="E52">
-        <v>812.25</v>
+        <v>829.159</v>
       </c>
       <c r="F52">
-        <v>845.45</v>
+        <v>862.359</v>
       </c>
       <c r="G52">
         <v>87.2</v>
@@ -5551,28 +5551,28 @@
         <v>288.91</v>
       </c>
       <c r="M52">
-        <v>45.907935</v>
+        <v>46.8260937</v>
       </c>
       <c r="N52">
-        <v>243.002065</v>
+        <v>242.0839063</v>
       </c>
       <c r="O52">
-        <v>72.9006195</v>
+        <v>72.62517189</v>
       </c>
       <c r="P52">
-        <v>170.1014455</v>
+        <v>169.45873441</v>
       </c>
       <c r="Q52">
-        <v>173.6914455</v>
+        <v>173.04873441</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1563995241449405</v>
+        <v>0.1582583396767883</v>
       </c>
       <c r="T52">
-        <v>0.9473716041163832</v>
+        <v>0.9632938159502721</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.293247561668806</v>
+        <v>6.169850550655692</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09693168644162627</v>
+        <v>0.09702261081078224</v>
       </c>
       <c r="C53">
-        <v>1068.667447599947</v>
+        <v>1049.990807955225</v>
       </c>
       <c r="D53">
-        <v>1843.826447599947</v>
+        <v>1842.058807955225</v>
       </c>
       <c r="E53">
-        <v>829.159</v>
+        <v>846.068</v>
       </c>
       <c r="F53">
-        <v>862.359</v>
+        <v>879.268</v>
       </c>
       <c r="G53">
         <v>87.2</v>
@@ -5633,45 +5633,45 @@
         <v>288.91</v>
       </c>
       <c r="M53">
-        <v>46.8260937</v>
+        <v>48.6235204</v>
       </c>
       <c r="N53">
-        <v>242.0839063</v>
+        <v>240.2864796</v>
       </c>
       <c r="O53">
-        <v>72.62517189</v>
+        <v>72.08594388</v>
       </c>
       <c r="P53">
-        <v>169.45873441</v>
+        <v>168.20053572</v>
       </c>
       <c r="Q53">
-        <v>173.04873441</v>
+        <v>171.79053572</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1582583396767883</v>
+        <v>0.1601946058557963</v>
       </c>
       <c r="T53">
-        <v>0.9632938159502721</v>
+        <v>0.9798794532772395</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.169850550655692</v>
+        <v>5.941774631357214</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09702261081078224</v>
+        <v>0.09675653517993822</v>
       </c>
       <c r="C54">
-        <v>1049.990807955225</v>
+        <v>1038.264102348527</v>
       </c>
       <c r="D54">
-        <v>1842.058807955225</v>
+        <v>1847.241102348527</v>
       </c>
       <c r="E54">
-        <v>846.068</v>
+        <v>862.9770000000001</v>
       </c>
       <c r="F54">
-        <v>879.268</v>
+        <v>896.1770000000001</v>
       </c>
       <c r="G54">
         <v>87.2</v>
@@ -5715,28 +5715,28 @@
         <v>288.91</v>
       </c>
       <c r="M54">
-        <v>48.6235204</v>
+        <v>49.55858810000001</v>
       </c>
       <c r="N54">
-        <v>240.2864796</v>
+        <v>239.3514119</v>
       </c>
       <c r="O54">
-        <v>72.08594388</v>
+        <v>71.80542357</v>
       </c>
       <c r="P54">
-        <v>168.20053572</v>
+        <v>167.54598833</v>
       </c>
       <c r="Q54">
-        <v>171.79053572</v>
+        <v>171.13598833</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1601946058557963</v>
+        <v>0.1622132663402941</v>
       </c>
       <c r="T54">
-        <v>0.9798794532772395</v>
+        <v>0.9971708624053546</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.941774631357214</v>
+        <v>5.829665676048587</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09675653517993822</v>
+        <v>0.09649045954909422</v>
       </c>
       <c r="C55">
-        <v>1038.264102348527</v>
+        <v>1026.566637874786</v>
       </c>
       <c r="D55">
-        <v>1847.241102348527</v>
+        <v>1852.452637874787</v>
       </c>
       <c r="E55">
-        <v>862.9770000000001</v>
+        <v>879.8860000000001</v>
       </c>
       <c r="F55">
-        <v>896.1770000000001</v>
+        <v>913.0860000000001</v>
       </c>
       <c r="G55">
         <v>87.2</v>
@@ -5797,28 +5797,28 @@
         <v>288.91</v>
       </c>
       <c r="M55">
-        <v>49.55858810000001</v>
+        <v>50.49365580000001</v>
       </c>
       <c r="N55">
-        <v>239.3514119</v>
+        <v>238.4163442</v>
       </c>
       <c r="O55">
-        <v>71.80542357</v>
+        <v>71.52490326</v>
       </c>
       <c r="P55">
-        <v>167.54598833</v>
+        <v>166.89144094</v>
       </c>
       <c r="Q55">
-        <v>171.13598833</v>
+        <v>170.48144094</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1622132663402941</v>
+        <v>0.164319694671944</v>
       </c>
       <c r="T55">
-        <v>0.9971708624053546</v>
+        <v>1.015214071930344</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.829665676048587</v>
+        <v>5.72170890426991</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09649045954909422</v>
+        <v>0.09622438391825019</v>
       </c>
       <c r="C56">
-        <v>1026.566637874786</v>
+        <v>1014.89866272416</v>
       </c>
       <c r="D56">
-        <v>1852.452637874787</v>
+        <v>1857.69366272416</v>
       </c>
       <c r="E56">
-        <v>879.8860000000001</v>
+        <v>896.7950000000001</v>
       </c>
       <c r="F56">
-        <v>913.0860000000001</v>
+        <v>929.9950000000001</v>
       </c>
       <c r="G56">
         <v>87.2</v>
@@ -5879,28 +5879,28 @@
         <v>288.91</v>
       </c>
       <c r="M56">
-        <v>50.49365580000001</v>
+        <v>51.42872350000001</v>
       </c>
       <c r="N56">
-        <v>238.4163442</v>
+        <v>237.4812765</v>
       </c>
       <c r="O56">
-        <v>71.52490326</v>
+        <v>71.24438295</v>
       </c>
       <c r="P56">
-        <v>166.89144094</v>
+        <v>166.23689355</v>
       </c>
       <c r="Q56">
-        <v>170.48144094</v>
+        <v>169.82689355</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.164319694671944</v>
+        <v>0.166519742040556</v>
       </c>
       <c r="T56">
-        <v>1.015214071930344</v>
+        <v>1.034059201878667</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.72170890426991</v>
+        <v>5.617677833283183</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09622438391825019</v>
+        <v>0.09595830828740619</v>
       </c>
       <c r="C57">
-        <v>1014.89866272416</v>
+        <v>1003.26042790353</v>
       </c>
       <c r="D57">
-        <v>1857.69366272416</v>
+        <v>1862.96442790353</v>
       </c>
       <c r="E57">
-        <v>896.7950000000001</v>
+        <v>913.7040000000001</v>
       </c>
       <c r="F57">
-        <v>929.9950000000001</v>
+        <v>946.9040000000001</v>
       </c>
       <c r="G57">
         <v>87.2</v>
@@ -5961,28 +5961,28 @@
         <v>288.91</v>
       </c>
       <c r="M57">
-        <v>51.42872350000001</v>
+        <v>52.36379120000001</v>
       </c>
       <c r="N57">
-        <v>237.4812765</v>
+        <v>236.5462088</v>
       </c>
       <c r="O57">
-        <v>71.24438295</v>
+        <v>70.96386264</v>
       </c>
       <c r="P57">
-        <v>166.23689355</v>
+        <v>165.58234616</v>
       </c>
       <c r="Q57">
-        <v>169.82689355</v>
+        <v>169.17234616</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.166519742040556</v>
+        <v>0.1688197915622868</v>
       </c>
       <c r="T57">
-        <v>1.034059201878667</v>
+        <v>1.053760928642822</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.617677833283183</v>
+        <v>5.517362157688842</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09595830828740619</v>
+        <v>0.09569223265656217</v>
       </c>
       <c r="C58">
-        <v>1003.26042790353</v>
+        <v>991.6521872765718</v>
       </c>
       <c r="D58">
-        <v>1862.96442790353</v>
+        <v>1868.265187276572</v>
       </c>
       <c r="E58">
-        <v>913.7040000000001</v>
+        <v>930.6130000000001</v>
       </c>
       <c r="F58">
-        <v>946.9040000000001</v>
+        <v>963.8130000000001</v>
       </c>
       <c r="G58">
         <v>87.2</v>
@@ -6043,28 +6043,28 @@
         <v>288.91</v>
       </c>
       <c r="M58">
-        <v>52.36379120000001</v>
+        <v>53.29885890000001</v>
       </c>
       <c r="N58">
-        <v>236.5462088</v>
+        <v>235.6111411</v>
       </c>
       <c r="O58">
-        <v>70.96386264</v>
+        <v>70.68334233</v>
       </c>
       <c r="P58">
-        <v>165.58234616</v>
+        <v>164.92779877</v>
       </c>
       <c r="Q58">
-        <v>169.17234616</v>
+        <v>168.51779877</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1688197915622868</v>
+        <v>0.1712268201315399</v>
       </c>
       <c r="T58">
-        <v>1.053760928642822</v>
+        <v>1.074379014791357</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.517362157688842</v>
+        <v>5.420566330360968</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09569223265656217</v>
+        <v>0.09542615702571816</v>
       </c>
       <c r="C59">
-        <v>991.6521872765718</v>
+        <v>980.0741976045165</v>
       </c>
       <c r="D59">
-        <v>1868.265187276572</v>
+        <v>1873.596197604517</v>
       </c>
       <c r="E59">
-        <v>930.6130000000001</v>
+        <v>947.5220000000002</v>
       </c>
       <c r="F59">
-        <v>963.8130000000001</v>
+        <v>980.7220000000002</v>
       </c>
       <c r="G59">
         <v>87.2</v>
@@ -6125,28 +6125,28 @@
         <v>288.91</v>
       </c>
       <c r="M59">
-        <v>53.29885890000001</v>
+        <v>54.23392660000001</v>
       </c>
       <c r="N59">
-        <v>235.6111411</v>
+        <v>234.6760734</v>
       </c>
       <c r="O59">
-        <v>70.68334233</v>
+        <v>70.40282202</v>
       </c>
       <c r="P59">
-        <v>164.92779877</v>
+        <v>164.27325138</v>
       </c>
       <c r="Q59">
-        <v>168.51779877</v>
+        <v>167.86325138</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1712268201315399</v>
+        <v>0.1737484691088528</v>
       </c>
       <c r="T59">
-        <v>1.074379014791357</v>
+        <v>1.095978914566012</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.420566330360968</v>
+        <v>5.32710829018233</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09542615702571816</v>
+        <v>0.09516008139487414</v>
       </c>
       <c r="C60">
-        <v>980.0741976045167</v>
+        <v>968.5267185876086</v>
       </c>
       <c r="D60">
-        <v>1873.596197604517</v>
+        <v>1878.957718587608</v>
       </c>
       <c r="E60">
-        <v>947.5219999999999</v>
+        <v>964.4309999999999</v>
       </c>
       <c r="F60">
-        <v>980.722</v>
+        <v>997.631</v>
       </c>
       <c r="G60">
         <v>87.2</v>
@@ -6207,28 +6207,28 @@
         <v>288.91</v>
       </c>
       <c r="M60">
-        <v>54.2339266</v>
+        <v>55.1689943</v>
       </c>
       <c r="N60">
-        <v>234.6760734</v>
+        <v>233.7410057</v>
       </c>
       <c r="O60">
-        <v>70.40282202</v>
+        <v>70.12230171</v>
       </c>
       <c r="P60">
-        <v>164.27325138</v>
+        <v>163.61870399</v>
       </c>
       <c r="Q60">
-        <v>167.86325138</v>
+        <v>167.20870399</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1737484691088527</v>
+        <v>0.1763931253533516</v>
       </c>
       <c r="T60">
-        <v>1.095978914566012</v>
+        <v>1.118632467988211</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.32710829018233</v>
+        <v>5.236818319162291</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09516008139487414</v>
+        <v>0.09489400576403013</v>
       </c>
       <c r="C61">
-        <v>968.5267185876086</v>
+        <v>957.0100129072746</v>
       </c>
       <c r="D61">
-        <v>1878.957718587608</v>
+        <v>1884.350012907275</v>
       </c>
       <c r="E61">
-        <v>964.4309999999999</v>
+        <v>981.3399999999999</v>
       </c>
       <c r="F61">
-        <v>997.631</v>
+        <v>1014.54</v>
       </c>
       <c r="G61">
         <v>87.2</v>
@@ -6289,28 +6289,28 @@
         <v>288.91</v>
       </c>
       <c r="M61">
-        <v>55.1689943</v>
+        <v>56.104062</v>
       </c>
       <c r="N61">
-        <v>233.7410057</v>
+        <v>232.805938</v>
       </c>
       <c r="O61">
-        <v>70.12230171</v>
+        <v>69.8417814</v>
       </c>
       <c r="P61">
-        <v>163.61870399</v>
+        <v>162.9641566</v>
       </c>
       <c r="Q61">
-        <v>167.20870399</v>
+        <v>166.5541566</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1763931253533516</v>
+        <v>0.1791700144100754</v>
       </c>
       <c r="T61">
-        <v>1.118632467988211</v>
+        <v>1.142418699081521</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.236818319162291</v>
+        <v>5.149538013842919</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09489400576403013</v>
+        <v>0.09462793013318613</v>
       </c>
       <c r="C62">
-        <v>957.0100129072746</v>
+        <v>945.5243462690294</v>
       </c>
       <c r="D62">
-        <v>1884.350012907275</v>
+        <v>1889.773346269029</v>
       </c>
       <c r="E62">
-        <v>981.3399999999999</v>
+        <v>998.249</v>
       </c>
       <c r="F62">
-        <v>1014.54</v>
+        <v>1031.449</v>
       </c>
       <c r="G62">
         <v>87.2</v>
@@ -6371,28 +6371,28 @@
         <v>288.91</v>
       </c>
       <c r="M62">
-        <v>56.104062</v>
+        <v>57.0391297</v>
       </c>
       <c r="N62">
-        <v>232.805938</v>
+        <v>231.8708703</v>
       </c>
       <c r="O62">
-        <v>69.8417814</v>
+        <v>69.56126109</v>
       </c>
       <c r="P62">
-        <v>162.9641566</v>
+        <v>162.30960921</v>
       </c>
       <c r="Q62">
-        <v>166.5541566</v>
+        <v>165.89960921</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1791700144100754</v>
+        <v>0.1820893080338106</v>
       </c>
       <c r="T62">
-        <v>1.142418699081521</v>
+        <v>1.167424736897564</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.149538013842919</v>
+        <v>5.065119357878282</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09462793013318613</v>
+        <v>0.09436185450234211</v>
       </c>
       <c r="C63">
-        <v>945.5243462690294</v>
+        <v>934.0699874461163</v>
       </c>
       <c r="D63">
-        <v>1889.773346269029</v>
+        <v>1895.227987446116</v>
       </c>
       <c r="E63">
-        <v>998.249</v>
+        <v>1015.158</v>
       </c>
       <c r="F63">
-        <v>1031.449</v>
+        <v>1048.358</v>
       </c>
       <c r="G63">
         <v>87.2</v>
@@ -6453,28 +6453,28 @@
         <v>288.91</v>
       </c>
       <c r="M63">
-        <v>57.0391297</v>
+        <v>57.9741974</v>
       </c>
       <c r="N63">
-        <v>231.8708703</v>
+        <v>230.9358026</v>
       </c>
       <c r="O63">
-        <v>69.56126109</v>
+        <v>69.28074078</v>
       </c>
       <c r="P63">
-        <v>162.30960921</v>
+        <v>161.65506182</v>
       </c>
       <c r="Q63">
-        <v>165.89960921</v>
+        <v>165.24506182</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1820893080338106</v>
+        <v>0.185162248690374</v>
       </c>
       <c r="T63">
-        <v>1.167424736897564</v>
+        <v>1.193746881967083</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.065119357878282</v>
+        <v>4.983423884364115</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09436185450234211</v>
+        <v>0.0940957788714981</v>
       </c>
       <c r="C64">
-        <v>934.0699874461163</v>
+        <v>922.6472083239087</v>
       </c>
       <c r="D64">
-        <v>1895.227987446116</v>
+        <v>1900.714208323909</v>
       </c>
       <c r="E64">
-        <v>1015.158</v>
+        <v>1032.067</v>
       </c>
       <c r="F64">
-        <v>1048.358</v>
+        <v>1065.267</v>
       </c>
       <c r="G64">
         <v>87.2</v>
@@ -6535,28 +6535,28 @@
         <v>288.91</v>
       </c>
       <c r="M64">
-        <v>57.9741974</v>
+        <v>58.90926510000001</v>
       </c>
       <c r="N64">
-        <v>230.9358026</v>
+        <v>230.0007349</v>
       </c>
       <c r="O64">
-        <v>69.28074078</v>
+        <v>69.00022047</v>
       </c>
       <c r="P64">
-        <v>161.65506182</v>
+        <v>161.00051443</v>
       </c>
       <c r="Q64">
-        <v>165.24506182</v>
+        <v>164.59051443</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.185162248690374</v>
+        <v>0.1884012942472922</v>
       </c>
       <c r="T64">
-        <v>1.193746881967083</v>
+        <v>1.221491845689009</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.983423884364115</v>
+        <v>4.904321917945637</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0940957788714981</v>
+        <v>0.09382970324065408</v>
       </c>
       <c r="C65">
-        <v>922.6472083239087</v>
+        <v>911.2562839450877</v>
       </c>
       <c r="D65">
-        <v>1900.714208323909</v>
+        <v>1906.232283945088</v>
       </c>
       <c r="E65">
-        <v>1032.067</v>
+        <v>1048.976</v>
       </c>
       <c r="F65">
-        <v>1065.267</v>
+        <v>1082.176</v>
       </c>
       <c r="G65">
         <v>87.2</v>
@@ -6617,28 +6617,28 @@
         <v>288.91</v>
       </c>
       <c r="M65">
-        <v>58.90926510000001</v>
+        <v>59.84433280000001</v>
       </c>
       <c r="N65">
-        <v>230.0007349</v>
+        <v>229.0656672</v>
       </c>
       <c r="O65">
-        <v>69.00022047</v>
+        <v>68.71970016</v>
       </c>
       <c r="P65">
-        <v>161.00051443</v>
+        <v>160.34596704</v>
       </c>
       <c r="Q65">
-        <v>164.59051443</v>
+        <v>163.93596704</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1884012942472922</v>
+        <v>0.1918202867795947</v>
       </c>
       <c r="T65">
-        <v>1.221491845689009</v>
+        <v>1.250778196284375</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.904321917945637</v>
+        <v>4.827691887977736</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09382970324065408</v>
+        <v>0.09356362760981007</v>
       </c>
       <c r="C66">
-        <v>911.2562839450877</v>
+        <v>899.8974925556024</v>
       </c>
       <c r="D66">
-        <v>1906.232283945088</v>
+        <v>1911.782492555602</v>
       </c>
       <c r="E66">
-        <v>1048.976</v>
+        <v>1065.885</v>
       </c>
       <c r="F66">
-        <v>1082.176</v>
+        <v>1099.085</v>
       </c>
       <c r="G66">
         <v>87.2</v>
@@ -6699,28 +6699,28 @@
         <v>288.91</v>
       </c>
       <c r="M66">
-        <v>59.84433280000001</v>
+        <v>60.7794005</v>
       </c>
       <c r="N66">
-        <v>229.0656672</v>
+        <v>228.1305995</v>
       </c>
       <c r="O66">
-        <v>68.71970016</v>
+        <v>68.43917985</v>
       </c>
       <c r="P66">
-        <v>160.34596704</v>
+        <v>159.69141965</v>
       </c>
       <c r="Q66">
-        <v>163.93596704</v>
+        <v>163.28141965</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1918202867795947</v>
+        <v>0.1954346503137431</v>
       </c>
       <c r="T66">
-        <v>1.250778196284375</v>
+        <v>1.281738052628048</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.827691887977736</v>
+        <v>4.753419705085772</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09356362760981007</v>
+        <v>0.09329755197896607</v>
       </c>
       <c r="C67">
-        <v>899.8974925556024</v>
+        <v>888.5711156514433</v>
       </c>
       <c r="D67">
-        <v>1911.782492555602</v>
+        <v>1917.365115651443</v>
       </c>
       <c r="E67">
-        <v>1065.885</v>
+        <v>1082.794</v>
       </c>
       <c r="F67">
-        <v>1099.085</v>
+        <v>1115.994</v>
       </c>
       <c r="G67">
         <v>87.2</v>
@@ -6781,28 +6781,28 @@
         <v>288.91</v>
       </c>
       <c r="M67">
-        <v>60.7794005</v>
+        <v>61.71446820000001</v>
       </c>
       <c r="N67">
-        <v>228.1305995</v>
+        <v>227.1955318</v>
       </c>
       <c r="O67">
-        <v>68.43917985</v>
+        <v>68.15865954</v>
       </c>
       <c r="P67">
-        <v>159.69141965</v>
+        <v>159.03687226</v>
       </c>
       <c r="Q67">
-        <v>163.28141965</v>
+        <v>162.62687226</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1954346503137431</v>
+        <v>0.1992616234675472</v>
       </c>
       <c r="T67">
-        <v>1.281738052628048</v>
+        <v>1.314519076991937</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.753419705085772</v>
+        <v>4.681398194402654</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09329755197896607</v>
+        <v>0.09303147634812205</v>
       </c>
       <c r="C68">
-        <v>888.5711156514433</v>
+        <v>877.2774380262319</v>
       </c>
       <c r="D68">
-        <v>1917.365115651443</v>
+        <v>1922.980438026232</v>
       </c>
       <c r="E68">
-        <v>1082.794</v>
+        <v>1099.703</v>
       </c>
       <c r="F68">
-        <v>1115.994</v>
+        <v>1132.903</v>
       </c>
       <c r="G68">
         <v>87.2</v>
@@ -6863,28 +6863,28 @@
         <v>288.91</v>
       </c>
       <c r="M68">
-        <v>61.71446820000001</v>
+        <v>62.6495359</v>
       </c>
       <c r="N68">
-        <v>227.1955318</v>
+        <v>226.2604641</v>
       </c>
       <c r="O68">
-        <v>68.15865954</v>
+        <v>67.87813923</v>
       </c>
       <c r="P68">
-        <v>159.03687226</v>
+        <v>158.38232487</v>
       </c>
       <c r="Q68">
-        <v>162.62687226</v>
+        <v>161.9723248700001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1992616234675472</v>
+        <v>0.2033205343882487</v>
       </c>
       <c r="T68">
-        <v>1.314519076991937</v>
+        <v>1.349286830105152</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.681398194402654</v>
+        <v>4.611526579560824</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09303147634812205</v>
+        <v>0.09276540071727804</v>
       </c>
       <c r="C69">
-        <v>877.2774380262319</v>
+        <v>866.016747819649</v>
       </c>
       <c r="D69">
-        <v>1922.980438026232</v>
+        <v>1928.628747819649</v>
       </c>
       <c r="E69">
-        <v>1099.703</v>
+        <v>1116.612</v>
       </c>
       <c r="F69">
-        <v>1132.903</v>
+        <v>1149.812</v>
       </c>
       <c r="G69">
         <v>87.2</v>
@@ -6945,28 +6945,28 @@
         <v>288.91</v>
       </c>
       <c r="M69">
-        <v>62.6495359</v>
+        <v>63.58460360000001</v>
       </c>
       <c r="N69">
-        <v>226.2604641</v>
+        <v>225.3253964</v>
       </c>
       <c r="O69">
-        <v>67.87813923</v>
+        <v>67.59761892</v>
       </c>
       <c r="P69">
-        <v>158.38232487</v>
+        <v>157.72777748</v>
       </c>
       <c r="Q69">
-        <v>161.9723248700001</v>
+        <v>161.31777748</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2033205343882487</v>
+        <v>0.2076331272414939</v>
       </c>
       <c r="T69">
-        <v>1.349286830105152</v>
+        <v>1.386227567787943</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.611526579560824</v>
+        <v>4.543710012214341</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09276540071727804</v>
+        <v>0.09370682508643403</v>
       </c>
       <c r="C70">
-        <v>866.016747819649</v>
+        <v>829.2704524765397</v>
       </c>
       <c r="D70">
-        <v>1928.628747819649</v>
+        <v>1908.79145247654</v>
       </c>
       <c r="E70">
-        <v>1116.612</v>
+        <v>1133.521</v>
       </c>
       <c r="F70">
-        <v>1149.812</v>
+        <v>1166.721</v>
       </c>
       <c r="G70">
         <v>87.2</v>
@@ -7027,45 +7027,45 @@
         <v>288.91</v>
       </c>
       <c r="M70">
-        <v>63.58460360000001</v>
+        <v>67.43647380000002</v>
       </c>
       <c r="N70">
-        <v>225.3253964</v>
+        <v>221.4735262</v>
       </c>
       <c r="O70">
-        <v>67.59761892</v>
+        <v>66.44205786000001</v>
       </c>
       <c r="P70">
-        <v>157.72777748</v>
+        <v>155.03146834</v>
       </c>
       <c r="Q70">
-        <v>161.31777748</v>
+        <v>158.62146834</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2076331272414939</v>
+        <v>0.2122239518917227</v>
       </c>
       <c r="T70">
-        <v>1.386227567787943</v>
+        <v>1.425551578869624</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.3</v>
       </c>
       <c r="W70">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.543710012214341</v>
+        <v>4.284180113818465</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09370682508643403</v>
+        <v>0.09345824945559</v>
       </c>
       <c r="C71">
-        <v>829.2704524765397</v>
+        <v>817.5595749227616</v>
       </c>
       <c r="D71">
-        <v>1908.79145247654</v>
+        <v>1913.989574922762</v>
       </c>
       <c r="E71">
-        <v>1133.521</v>
+        <v>1150.43</v>
       </c>
       <c r="F71">
-        <v>1166.721</v>
+        <v>1183.63</v>
       </c>
       <c r="G71">
         <v>87.2</v>
@@ -7109,28 +7109,28 @@
         <v>288.91</v>
       </c>
       <c r="M71">
-        <v>67.43647380000002</v>
+        <v>68.41381400000002</v>
       </c>
       <c r="N71">
-        <v>221.4735262</v>
+        <v>220.496186</v>
       </c>
       <c r="O71">
-        <v>66.44205786000001</v>
+        <v>66.14885580000001</v>
       </c>
       <c r="P71">
-        <v>155.03146834</v>
+        <v>154.3473302</v>
       </c>
       <c r="Q71">
-        <v>158.62146834</v>
+        <v>157.9373302</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2122239518917227</v>
+        <v>0.2171208315186334</v>
       </c>
       <c r="T71">
-        <v>1.425551578869624</v>
+        <v>1.467497190690084</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.284180113818465</v>
+        <v>4.222977540763916</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09345824945559</v>
+        <v>0.093209673824746</v>
       </c>
       <c r="C72">
-        <v>817.5595749227616</v>
+        <v>805.8770862864467</v>
       </c>
       <c r="D72">
-        <v>1913.989574922762</v>
+        <v>1919.216086286447</v>
       </c>
       <c r="E72">
-        <v>1150.43</v>
+        <v>1167.339</v>
       </c>
       <c r="F72">
-        <v>1183.63</v>
+        <v>1200.539</v>
       </c>
       <c r="G72">
         <v>87.2</v>
@@ -7191,28 +7191,28 @@
         <v>288.91</v>
       </c>
       <c r="M72">
-        <v>68.41381400000002</v>
+        <v>69.39115420000002</v>
       </c>
       <c r="N72">
-        <v>220.496186</v>
+        <v>219.5188458</v>
       </c>
       <c r="O72">
-        <v>66.14885580000001</v>
+        <v>65.85565373999999</v>
       </c>
       <c r="P72">
-        <v>154.3473302</v>
+        <v>153.66319206</v>
       </c>
       <c r="Q72">
-        <v>157.9373302</v>
+        <v>157.25319206</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2171208315186334</v>
+        <v>0.2223554269818828</v>
       </c>
       <c r="T72">
-        <v>1.467497190690084</v>
+        <v>1.512335603325748</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.222977540763916</v>
+        <v>4.163498983851748</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09320967382474601</v>
+        <v>0.09296109819390198</v>
       </c>
       <c r="C73">
-        <v>805.8770862864467</v>
+        <v>794.2232197683579</v>
       </c>
       <c r="D73">
-        <v>1919.216086286447</v>
+        <v>1924.471219768358</v>
       </c>
       <c r="E73">
-        <v>1167.339</v>
+        <v>1184.248</v>
       </c>
       <c r="F73">
-        <v>1200.539</v>
+        <v>1217.448</v>
       </c>
       <c r="G73">
         <v>87.2</v>
@@ -7273,28 +7273,28 @@
         <v>288.91</v>
       </c>
       <c r="M73">
-        <v>69.3911542</v>
+        <v>70.36849440000002</v>
       </c>
       <c r="N73">
-        <v>219.5188458</v>
+        <v>218.5415056</v>
       </c>
       <c r="O73">
-        <v>65.85565373999999</v>
+        <v>65.56245168</v>
       </c>
       <c r="P73">
-        <v>153.66319206</v>
+        <v>152.97905392</v>
       </c>
       <c r="Q73">
-        <v>157.25319206</v>
+        <v>156.56905392</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2223554269818828</v>
+        <v>0.2279639221210785</v>
       </c>
       <c r="T73">
-        <v>1.512335603325748</v>
+        <v>1.560376759721102</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.163498983851749</v>
+        <v>4.105672609076029</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09296109819390198</v>
+        <v>0.09271252256305798</v>
       </c>
       <c r="C74">
-        <v>794.2232197683579</v>
+        <v>782.5982111304384</v>
       </c>
       <c r="D74">
-        <v>1924.471219768358</v>
+        <v>1929.755211130438</v>
       </c>
       <c r="E74">
-        <v>1184.248</v>
+        <v>1201.157</v>
       </c>
       <c r="F74">
-        <v>1217.448</v>
+        <v>1234.357</v>
       </c>
       <c r="G74">
         <v>87.2</v>
@@ -7355,28 +7355,28 @@
         <v>288.91</v>
       </c>
       <c r="M74">
-        <v>70.36849440000002</v>
+        <v>71.3458346</v>
       </c>
       <c r="N74">
-        <v>218.5415056</v>
+        <v>217.5641654</v>
       </c>
       <c r="O74">
-        <v>65.56245168</v>
+        <v>65.26924962000001</v>
       </c>
       <c r="P74">
-        <v>152.97905392</v>
+        <v>152.29491578</v>
       </c>
       <c r="Q74">
-        <v>156.56905392</v>
+        <v>155.88491578</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2279639221210785</v>
+        <v>0.2339878613446592</v>
       </c>
       <c r="T74">
-        <v>1.560376759721102</v>
+        <v>1.611976520293889</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.105672609076029</v>
+        <v>4.049430518540742</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09271252256305798</v>
+        <v>0.09427694693221395</v>
       </c>
       <c r="C75">
-        <v>782.5982111304384</v>
+        <v>732.9092551321096</v>
       </c>
       <c r="D75">
-        <v>1929.755211130438</v>
+        <v>1896.97525513211</v>
       </c>
       <c r="E75">
-        <v>1201.157</v>
+        <v>1218.066</v>
       </c>
       <c r="F75">
-        <v>1234.357</v>
+        <v>1251.266</v>
       </c>
       <c r="G75">
         <v>87.2</v>
@@ -7437,45 +7437,45 @@
         <v>288.91</v>
       </c>
       <c r="M75">
-        <v>71.3458346</v>
+        <v>76.7026058</v>
       </c>
       <c r="N75">
-        <v>217.5641654</v>
+        <v>212.2073942</v>
       </c>
       <c r="O75">
-        <v>65.26924962000001</v>
+        <v>63.66221826</v>
       </c>
       <c r="P75">
-        <v>152.29491578</v>
+        <v>148.54517594</v>
       </c>
       <c r="Q75">
-        <v>155.88491578</v>
+        <v>152.13517594</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2339878613446592</v>
+        <v>0.2404751805085152</v>
       </c>
       <c r="T75">
-        <v>1.611976520293889</v>
+        <v>1.66754549321843</v>
       </c>
       <c r="U75">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V75">
         <v>0.3</v>
       </c>
       <c r="W75">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.049430518540742</v>
+        <v>3.766625618343725</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09427694693221395</v>
+        <v>0.09405287130136994</v>
       </c>
       <c r="C76">
-        <v>732.9092551321096</v>
+        <v>720.6268961207484</v>
       </c>
       <c r="D76">
-        <v>1896.97525513211</v>
+        <v>1901.601896120749</v>
       </c>
       <c r="E76">
-        <v>1218.066</v>
+        <v>1234.975</v>
       </c>
       <c r="F76">
-        <v>1251.266</v>
+        <v>1268.175</v>
       </c>
       <c r="G76">
         <v>87.2</v>
@@ -7519,28 +7519,28 @@
         <v>288.91</v>
       </c>
       <c r="M76">
-        <v>76.7026058</v>
+        <v>77.73912750000001</v>
       </c>
       <c r="N76">
-        <v>212.2073942</v>
+        <v>211.1708725</v>
       </c>
       <c r="O76">
-        <v>63.66221826</v>
+        <v>63.35126175000001</v>
       </c>
       <c r="P76">
-        <v>148.54517594</v>
+        <v>147.81961075</v>
       </c>
       <c r="Q76">
-        <v>152.13517594</v>
+        <v>151.40961075</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2404751805085152</v>
+        <v>0.2474814852054798</v>
       </c>
       <c r="T76">
-        <v>1.66754549321843</v>
+        <v>1.727559983976934</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.766625618343725</v>
+        <v>3.716403943432475</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09405287130136994</v>
+        <v>0.09382879567052593</v>
       </c>
       <c r="C77">
-        <v>720.6268961207484</v>
+        <v>708.3671606436326</v>
       </c>
       <c r="D77">
-        <v>1901.601896120749</v>
+        <v>1906.251160643633</v>
       </c>
       <c r="E77">
-        <v>1234.975</v>
+        <v>1251.884</v>
       </c>
       <c r="F77">
-        <v>1268.175</v>
+        <v>1285.084</v>
       </c>
       <c r="G77">
         <v>87.2</v>
@@ -7601,28 +7601,28 @@
         <v>288.91</v>
       </c>
       <c r="M77">
-        <v>77.73912750000001</v>
+        <v>78.7756492</v>
       </c>
       <c r="N77">
-        <v>211.1708725</v>
+        <v>210.1343508</v>
       </c>
       <c r="O77">
-        <v>63.35126175000001</v>
+        <v>63.04030524</v>
       </c>
       <c r="P77">
-        <v>147.81961075</v>
+        <v>147.09404556</v>
       </c>
       <c r="Q77">
-        <v>151.40961075</v>
+        <v>150.68404556</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2474814852054798</v>
+        <v>0.2550716486271914</v>
       </c>
       <c r="T77">
-        <v>1.727559983976934</v>
+        <v>1.792575682298647</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.716403943432475</v>
+        <v>3.667503891545206</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09382879567052593</v>
+        <v>0.0936047200396819</v>
       </c>
       <c r="C78">
-        <v>708.3671606436326</v>
+        <v>696.130215045657</v>
       </c>
       <c r="D78">
-        <v>1906.251160643633</v>
+        <v>1910.923215045657</v>
       </c>
       <c r="E78">
-        <v>1251.884</v>
+        <v>1268.793</v>
       </c>
       <c r="F78">
-        <v>1285.084</v>
+        <v>1301.993</v>
       </c>
       <c r="G78">
         <v>87.2</v>
@@ -7683,28 +7683,28 @@
         <v>288.91</v>
       </c>
       <c r="M78">
-        <v>78.7756492</v>
+        <v>79.81217090000001</v>
       </c>
       <c r="N78">
-        <v>210.1343508</v>
+        <v>209.0978291</v>
       </c>
       <c r="O78">
-        <v>63.04030524</v>
+        <v>62.72934873</v>
       </c>
       <c r="P78">
-        <v>147.09404556</v>
+        <v>146.36848037</v>
       </c>
       <c r="Q78">
-        <v>150.68404556</v>
+        <v>149.95848037</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2550716486271914</v>
+        <v>0.2633218262594866</v>
       </c>
       <c r="T78">
-        <v>1.792575682298647</v>
+        <v>1.863244919604856</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.667503891545206</v>
+        <v>3.619873970875787</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0936047200396819</v>
+        <v>0.09338064440883789</v>
       </c>
       <c r="C79">
-        <v>696.130215045657</v>
+        <v>683.9162273065085</v>
       </c>
       <c r="D79">
-        <v>1910.923215045657</v>
+        <v>1915.618227306509</v>
       </c>
       <c r="E79">
-        <v>1268.793</v>
+        <v>1285.702</v>
       </c>
       <c r="F79">
-        <v>1301.993</v>
+        <v>1318.902</v>
       </c>
       <c r="G79">
         <v>87.2</v>
@@ -7765,28 +7765,28 @@
         <v>288.91</v>
       </c>
       <c r="M79">
-        <v>79.81217090000001</v>
+        <v>80.84869260000001</v>
       </c>
       <c r="N79">
-        <v>209.0978291</v>
+        <v>208.0613074</v>
       </c>
       <c r="O79">
-        <v>62.72934873</v>
+        <v>62.41839222000001</v>
       </c>
       <c r="P79">
-        <v>146.36848037</v>
+        <v>145.64291518</v>
       </c>
       <c r="Q79">
-        <v>149.95848037</v>
+        <v>149.23291518</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2633218262594866</v>
+        <v>0.2723220200401723</v>
       </c>
       <c r="T79">
-        <v>1.863244919604856</v>
+        <v>1.940338633029812</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.619873970875787</v>
+        <v>3.573465330223534</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09338064440883789</v>
+        <v>0.09315656877799389</v>
       </c>
       <c r="C80">
-        <v>683.9162273065085</v>
+        <v>671.7253670608018</v>
       </c>
       <c r="D80">
-        <v>1915.618227306509</v>
+        <v>1920.336367060802</v>
       </c>
       <c r="E80">
-        <v>1285.702</v>
+        <v>1302.611</v>
       </c>
       <c r="F80">
-        <v>1318.902</v>
+        <v>1335.811</v>
       </c>
       <c r="G80">
         <v>87.2</v>
@@ -7847,28 +7847,28 @@
         <v>288.91</v>
       </c>
       <c r="M80">
-        <v>80.84869260000001</v>
+        <v>81.88521430000002</v>
       </c>
       <c r="N80">
-        <v>208.0613074</v>
+        <v>207.0247857</v>
       </c>
       <c r="O80">
-        <v>62.41839222000001</v>
+        <v>62.10743571</v>
       </c>
       <c r="P80">
-        <v>145.64291518</v>
+        <v>144.91734999</v>
       </c>
       <c r="Q80">
-        <v>149.23291518</v>
+        <v>148.50734999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2723220200401723</v>
+        <v>0.2821793751333043</v>
       </c>
       <c r="T80">
-        <v>1.940338633029812</v>
+        <v>2.024774604876192</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.573465330223534</v>
+        <v>3.528231591866274</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09315656877799389</v>
+        <v>0.09450049314714987</v>
       </c>
       <c r="C81">
-        <v>671.7253670608018</v>
+        <v>626.8619247528616</v>
       </c>
       <c r="D81">
-        <v>1920.336367060802</v>
+        <v>1892.381924752862</v>
       </c>
       <c r="E81">
-        <v>1302.611</v>
+        <v>1319.52</v>
       </c>
       <c r="F81">
-        <v>1335.811</v>
+        <v>1352.72</v>
       </c>
       <c r="G81">
         <v>87.2</v>
@@ -7929,45 +7929,45 @@
         <v>288.91</v>
       </c>
       <c r="M81">
-        <v>81.88521430000002</v>
+        <v>86.70935200000002</v>
       </c>
       <c r="N81">
-        <v>207.0247857</v>
+        <v>202.200648</v>
       </c>
       <c r="O81">
-        <v>62.10743571</v>
+        <v>60.66019439999999</v>
       </c>
       <c r="P81">
-        <v>144.91734999</v>
+        <v>141.5404536</v>
       </c>
       <c r="Q81">
-        <v>148.50734999</v>
+        <v>145.1304536</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2821793751333043</v>
+        <v>0.2930224657357494</v>
       </c>
       <c r="T81">
-        <v>2.024774604876192</v>
+        <v>2.117654173907209</v>
       </c>
       <c r="U81">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V81">
         <v>0.3</v>
       </c>
       <c r="W81">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.528231591866274</v>
+        <v>3.331935867771217</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09450049314714987</v>
+        <v>0.09429601751630587</v>
       </c>
       <c r="C82">
-        <v>626.8619247528616</v>
+        <v>614.1535312497704</v>
       </c>
       <c r="D82">
-        <v>1892.381924752862</v>
+        <v>1896.58253124977</v>
       </c>
       <c r="E82">
-        <v>1319.52</v>
+        <v>1336.429</v>
       </c>
       <c r="F82">
-        <v>1352.72</v>
+        <v>1369.629</v>
       </c>
       <c r="G82">
         <v>87.2</v>
@@ -8011,28 +8011,28 @@
         <v>288.91</v>
       </c>
       <c r="M82">
-        <v>86.70935200000002</v>
+        <v>87.79321890000001</v>
       </c>
       <c r="N82">
-        <v>202.200648</v>
+        <v>201.1167811</v>
       </c>
       <c r="O82">
-        <v>60.66019439999999</v>
+        <v>60.33503433000001</v>
       </c>
       <c r="P82">
-        <v>141.5404536</v>
+        <v>140.78174677</v>
       </c>
       <c r="Q82">
-        <v>145.1304536</v>
+        <v>144.37174677</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2930224657357494</v>
+        <v>0.3050069342963467</v>
       </c>
       <c r="T82">
-        <v>2.117654173907209</v>
+        <v>2.220310539678335</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.331935867771217</v>
+        <v>3.290800857057993</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09429601751630587</v>
+        <v>0.09409154188546186</v>
       </c>
       <c r="C83">
-        <v>614.1535312497704</v>
+        <v>601.4638277896017</v>
       </c>
       <c r="D83">
-        <v>1896.58253124977</v>
+        <v>1900.801827789602</v>
       </c>
       <c r="E83">
-        <v>1336.429</v>
+        <v>1353.338</v>
       </c>
       <c r="F83">
-        <v>1369.629</v>
+        <v>1386.538</v>
       </c>
       <c r="G83">
         <v>87.2</v>
@@ -8093,28 +8093,28 @@
         <v>288.91</v>
       </c>
       <c r="M83">
-        <v>87.79321890000001</v>
+        <v>88.87708580000002</v>
       </c>
       <c r="N83">
-        <v>201.1167811</v>
+        <v>200.0329142</v>
       </c>
       <c r="O83">
-        <v>60.33503433000001</v>
+        <v>60.00987426</v>
       </c>
       <c r="P83">
-        <v>140.78174677</v>
+        <v>140.02303994</v>
       </c>
       <c r="Q83">
-        <v>144.37174677</v>
+        <v>143.61303994</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3050069342963467</v>
+        <v>0.3183230104747882</v>
       </c>
       <c r="T83">
-        <v>2.220310539678335</v>
+        <v>2.334373168312919</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.290800857057993</v>
+        <v>3.250669139288993</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09409154188546186</v>
+        <v>0.09388706625461783</v>
       </c>
       <c r="C84">
-        <v>601.4638277896017</v>
+        <v>588.7929393887887</v>
       </c>
       <c r="D84">
-        <v>1900.801827789602</v>
+        <v>1905.039939388789</v>
       </c>
       <c r="E84">
-        <v>1353.338</v>
+        <v>1370.247</v>
       </c>
       <c r="F84">
-        <v>1386.538</v>
+        <v>1403.447</v>
       </c>
       <c r="G84">
         <v>87.2</v>
@@ -8175,28 +8175,28 @@
         <v>288.91</v>
       </c>
       <c r="M84">
-        <v>88.87708580000002</v>
+        <v>89.96095270000001</v>
       </c>
       <c r="N84">
-        <v>200.0329142</v>
+        <v>198.9490473</v>
       </c>
       <c r="O84">
-        <v>60.00987426</v>
+        <v>59.68471419</v>
       </c>
       <c r="P84">
-        <v>140.02303994</v>
+        <v>139.26433311</v>
       </c>
       <c r="Q84">
-        <v>143.61303994</v>
+        <v>142.85433311</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3183230104747882</v>
+        <v>0.3332056838506933</v>
       </c>
       <c r="T84">
-        <v>2.334373168312919</v>
+        <v>2.461854929728041</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.250669139288993</v>
+        <v>3.211504450863825</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09388706625461783</v>
+        <v>0.09368259062377382</v>
       </c>
       <c r="C85">
-        <v>588.7929393887887</v>
+        <v>576.1409921812226</v>
       </c>
       <c r="D85">
-        <v>1905.039939388789</v>
+        <v>1909.296992181223</v>
       </c>
       <c r="E85">
-        <v>1370.247</v>
+        <v>1387.156</v>
       </c>
       <c r="F85">
-        <v>1403.447</v>
+        <v>1420.356</v>
       </c>
       <c r="G85">
         <v>87.2</v>
@@ -8257,28 +8257,28 @@
         <v>288.91</v>
       </c>
       <c r="M85">
-        <v>89.96095270000001</v>
+        <v>91.04481960000003</v>
       </c>
       <c r="N85">
-        <v>198.9490473</v>
+        <v>197.8651804</v>
       </c>
       <c r="O85">
-        <v>59.68471419</v>
+        <v>59.35955411999999</v>
       </c>
       <c r="P85">
-        <v>139.26433311</v>
+        <v>138.50562628</v>
       </c>
       <c r="Q85">
-        <v>142.85433311</v>
+        <v>142.09562628</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3332056838506933</v>
+        <v>0.3499486913985866</v>
       </c>
       <c r="T85">
-        <v>2.461854929728041</v>
+        <v>2.605271911320055</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.211504450863825</v>
+        <v>3.173272255020207</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09368259062377383</v>
+        <v>0.09347811499292982</v>
       </c>
       <c r="C86">
-        <v>576.1409921812224</v>
+        <v>563.5081134307695</v>
       </c>
       <c r="D86">
-        <v>1909.296992181222</v>
+        <v>1913.57311343077</v>
       </c>
       <c r="E86">
-        <v>1387.156</v>
+        <v>1404.065</v>
       </c>
       <c r="F86">
-        <v>1420.356</v>
+        <v>1437.265</v>
       </c>
       <c r="G86">
         <v>87.2</v>
@@ -8339,28 +8339,28 @@
         <v>288.91</v>
       </c>
       <c r="M86">
-        <v>91.04481960000001</v>
+        <v>92.12868650000001</v>
       </c>
       <c r="N86">
-        <v>197.8651804</v>
+        <v>196.7813135</v>
       </c>
       <c r="O86">
-        <v>59.35955412</v>
+        <v>59.03439405</v>
       </c>
       <c r="P86">
-        <v>138.50562628</v>
+        <v>137.74691945</v>
       </c>
       <c r="Q86">
-        <v>142.09562628</v>
+        <v>141.33691945</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3499486913985864</v>
+        <v>0.3689240999528655</v>
       </c>
       <c r="T86">
-        <v>2.605271911320053</v>
+        <v>2.767811157124335</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.173272255020207</v>
+        <v>3.135939640255264</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09347811499292982</v>
+        <v>0.0932736393620858</v>
       </c>
       <c r="C87">
-        <v>563.5081134307695</v>
+        <v>550.8944315439524</v>
       </c>
       <c r="D87">
-        <v>1913.57311343077</v>
+        <v>1917.868431543952</v>
       </c>
       <c r="E87">
-        <v>1404.065</v>
+        <v>1420.974</v>
       </c>
       <c r="F87">
-        <v>1437.265</v>
+        <v>1454.174</v>
       </c>
       <c r="G87">
         <v>87.2</v>
@@ -8421,28 +8421,28 @@
         <v>288.91</v>
       </c>
       <c r="M87">
-        <v>92.12868650000001</v>
+        <v>93.2125534</v>
       </c>
       <c r="N87">
-        <v>196.7813135</v>
+        <v>195.6974466</v>
       </c>
       <c r="O87">
-        <v>59.03439405</v>
+        <v>58.70923398000001</v>
       </c>
       <c r="P87">
-        <v>137.74691945</v>
+        <v>136.98821262</v>
       </c>
       <c r="Q87">
-        <v>141.33691945</v>
+        <v>140.57821262</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3689240999528655</v>
+        <v>0.3906102811577557</v>
       </c>
       <c r="T87">
-        <v>2.767811157124335</v>
+        <v>2.95357029518637</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.135939640255264</v>
+        <v>3.099475225833691</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0932736393620858</v>
+        <v>0.0930691637312418</v>
       </c>
       <c r="C88">
-        <v>550.8944315439524</v>
+        <v>538.3000760828008</v>
       </c>
       <c r="D88">
-        <v>1917.868431543952</v>
+        <v>1922.183076082801</v>
       </c>
       <c r="E88">
-        <v>1420.974</v>
+        <v>1437.883</v>
       </c>
       <c r="F88">
-        <v>1454.174</v>
+        <v>1471.083</v>
       </c>
       <c r="G88">
         <v>87.2</v>
@@ -8503,28 +8503,28 @@
         <v>288.91</v>
       </c>
       <c r="M88">
-        <v>93.2125534</v>
+        <v>94.29642030000001</v>
       </c>
       <c r="N88">
-        <v>195.6974466</v>
+        <v>194.6135797</v>
       </c>
       <c r="O88">
-        <v>58.70923398000001</v>
+        <v>58.38407391</v>
       </c>
       <c r="P88">
-        <v>136.98821262</v>
+        <v>136.22950579</v>
       </c>
       <c r="Q88">
-        <v>140.57821262</v>
+        <v>139.81950579</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3906102811577557</v>
+        <v>0.4156327979326291</v>
       </c>
       <c r="T88">
-        <v>2.95357029518637</v>
+        <v>3.167907762181028</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.099475225833691</v>
+        <v>3.063849073812614</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0930691637312418</v>
+        <v>0.09286468810039779</v>
       </c>
       <c r="C89">
-        <v>538.3000760828008</v>
+        <v>525.7251777778818</v>
       </c>
       <c r="D89">
-        <v>1922.183076082801</v>
+        <v>1926.517177777882</v>
       </c>
       <c r="E89">
-        <v>1437.883</v>
+        <v>1454.792</v>
       </c>
       <c r="F89">
-        <v>1471.083</v>
+        <v>1487.992</v>
       </c>
       <c r="G89">
         <v>87.2</v>
@@ -8585,28 +8585,28 @@
         <v>288.91</v>
       </c>
       <c r="M89">
-        <v>94.29642030000001</v>
+        <v>95.38028720000001</v>
       </c>
       <c r="N89">
-        <v>194.6135797</v>
+        <v>193.5297128</v>
       </c>
       <c r="O89">
-        <v>58.38407391</v>
+        <v>58.05891384</v>
       </c>
       <c r="P89">
-        <v>136.22950579</v>
+        <v>135.47079896</v>
       </c>
       <c r="Q89">
-        <v>139.81950579</v>
+        <v>139.06079896</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4156327979326291</v>
+        <v>0.4448257341699816</v>
       </c>
       <c r="T89">
-        <v>3.167907762181028</v>
+        <v>3.417968140341461</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.063849073812614</v>
+        <v>3.029032607064744</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09286468810039779</v>
+        <v>0.09751961246955376</v>
       </c>
       <c r="C90">
-        <v>525.7251777778818</v>
+        <v>414.7552959143075</v>
       </c>
       <c r="D90">
-        <v>1926.517177777882</v>
+        <v>1832.456295914307</v>
       </c>
       <c r="E90">
-        <v>1454.792</v>
+        <v>1471.701</v>
       </c>
       <c r="F90">
-        <v>1487.992</v>
+        <v>1504.901</v>
       </c>
       <c r="G90">
         <v>87.2</v>
@@ -8667,45 +8667,45 @@
         <v>288.91</v>
       </c>
       <c r="M90">
-        <v>95.38028720000001</v>
+        <v>108.2023819</v>
       </c>
       <c r="N90">
-        <v>193.5297128</v>
+        <v>180.7076181</v>
       </c>
       <c r="O90">
-        <v>58.05891384</v>
+        <v>54.21228542999999</v>
       </c>
       <c r="P90">
-        <v>135.47079896</v>
+        <v>126.49533267</v>
       </c>
       <c r="Q90">
-        <v>139.06079896</v>
+        <v>130.08533267</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4448257341699816</v>
+        <v>0.4793264769959434</v>
       </c>
       <c r="T90">
-        <v>3.417968140341461</v>
+        <v>3.713494041803791</v>
       </c>
       <c r="U90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V90">
         <v>0.3</v>
       </c>
       <c r="W90">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.029032607064744</v>
+        <v>2.670089095330719</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09751961246955376</v>
+        <v>0.09736973683870975</v>
       </c>
       <c r="C91">
-        <v>414.7552959143075</v>
+        <v>400.7314660760771</v>
       </c>
       <c r="D91">
-        <v>1832.456295914307</v>
+        <v>1835.341466076077</v>
       </c>
       <c r="E91">
-        <v>1471.701</v>
+        <v>1488.61</v>
       </c>
       <c r="F91">
-        <v>1504.901</v>
+        <v>1521.81</v>
       </c>
       <c r="G91">
         <v>87.2</v>
@@ -8749,28 +8749,28 @@
         <v>288.91</v>
       </c>
       <c r="M91">
-        <v>108.2023819</v>
+        <v>109.418139</v>
       </c>
       <c r="N91">
-        <v>180.7076181</v>
+        <v>179.491861</v>
       </c>
       <c r="O91">
-        <v>54.21228542999999</v>
+        <v>53.8475583</v>
       </c>
       <c r="P91">
-        <v>126.49533267</v>
+        <v>125.6443027</v>
       </c>
       <c r="Q91">
-        <v>130.08533267</v>
+        <v>129.2343027</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4793264769959434</v>
+        <v>0.5207273683870975</v>
       </c>
       <c r="T91">
-        <v>3.713494041803791</v>
+        <v>4.068125123558587</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.670089095330719</v>
+        <v>2.640421438715933</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09736973683870975</v>
+        <v>0.09721986120786574</v>
       </c>
       <c r="C92">
-        <v>400.7314660760771</v>
+        <v>386.7167358642514</v>
       </c>
       <c r="D92">
-        <v>1835.341466076077</v>
+        <v>1838.235735864251</v>
       </c>
       <c r="E92">
-        <v>1488.61</v>
+        <v>1505.519</v>
       </c>
       <c r="F92">
-        <v>1521.81</v>
+        <v>1538.719</v>
       </c>
       <c r="G92">
         <v>87.2</v>
@@ -8831,28 +8831,28 @@
         <v>288.91</v>
       </c>
       <c r="M92">
-        <v>109.418139</v>
+        <v>110.6338961</v>
       </c>
       <c r="N92">
-        <v>179.491861</v>
+        <v>178.2761039</v>
       </c>
       <c r="O92">
-        <v>53.8475583</v>
+        <v>53.48283117</v>
       </c>
       <c r="P92">
-        <v>125.6443027</v>
+        <v>124.79327273</v>
       </c>
       <c r="Q92">
-        <v>129.2343027</v>
+        <v>128.38327273</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5207273683870975</v>
+        <v>0.5713284578651751</v>
       </c>
       <c r="T92">
-        <v>4.068125123558587</v>
+        <v>4.501563112370005</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.640421438715933</v>
+        <v>2.611405818510264</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09721986120786574</v>
+        <v>0.09706998557702173</v>
       </c>
       <c r="C93">
-        <v>386.7167358642514</v>
+        <v>372.7111483962096</v>
       </c>
       <c r="D93">
-        <v>1838.235735864251</v>
+        <v>1841.13914839621</v>
       </c>
       <c r="E93">
-        <v>1505.519</v>
+        <v>1522.428</v>
       </c>
       <c r="F93">
-        <v>1538.719</v>
+        <v>1555.628</v>
       </c>
       <c r="G93">
         <v>87.2</v>
@@ -8913,28 +8913,28 @@
         <v>288.91</v>
       </c>
       <c r="M93">
-        <v>110.6338961</v>
+        <v>111.8496532</v>
       </c>
       <c r="N93">
-        <v>178.2761039</v>
+        <v>177.0603468</v>
       </c>
       <c r="O93">
-        <v>53.48283117</v>
+        <v>53.11810404</v>
       </c>
       <c r="P93">
-        <v>124.79327273</v>
+        <v>123.94224276</v>
       </c>
       <c r="Q93">
-        <v>128.38327273</v>
+        <v>127.53224276</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5713284578651751</v>
+        <v>0.6345798197127719</v>
       </c>
       <c r="T93">
-        <v>4.501563112370005</v>
+        <v>5.043360598384278</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.611405818510264</v>
+        <v>2.583020972656891</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09706998557702173</v>
+        <v>0.09692010994617771</v>
       </c>
       <c r="C94">
-        <v>372.7111483962096</v>
+        <v>358.714747062171</v>
       </c>
       <c r="D94">
-        <v>1841.13914839621</v>
+        <v>1844.051747062171</v>
       </c>
       <c r="E94">
-        <v>1522.428</v>
+        <v>1539.337</v>
       </c>
       <c r="F94">
-        <v>1555.628</v>
+        <v>1572.537</v>
       </c>
       <c r="G94">
         <v>87.2</v>
@@ -8995,28 +8995,28 @@
         <v>288.91</v>
       </c>
       <c r="M94">
-        <v>111.8496532</v>
+        <v>113.0654103</v>
       </c>
       <c r="N94">
-        <v>177.0603468</v>
+        <v>175.8445897</v>
       </c>
       <c r="O94">
-        <v>53.11810404</v>
+        <v>52.75337691</v>
       </c>
       <c r="P94">
-        <v>123.94224276</v>
+        <v>123.09121279</v>
       </c>
       <c r="Q94">
-        <v>127.53224276</v>
+        <v>126.68121279</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6345798197127719</v>
+        <v>0.7159029992311106</v>
       </c>
       <c r="T94">
-        <v>5.043360598384278</v>
+        <v>5.739957366116913</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.583020972656891</v>
+        <v>2.555246553596064</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09692010994617771</v>
+        <v>0.0967702343153337</v>
       </c>
       <c r="C95">
-        <v>358.714747062171</v>
+        <v>344.7275755273536</v>
       </c>
       <c r="D95">
-        <v>1844.051747062171</v>
+        <v>1846.973575527354</v>
       </c>
       <c r="E95">
-        <v>1539.337</v>
+        <v>1556.246</v>
       </c>
       <c r="F95">
-        <v>1572.537</v>
+        <v>1589.446</v>
       </c>
       <c r="G95">
         <v>87.2</v>
@@ -9077,28 +9077,28 @@
         <v>288.91</v>
       </c>
       <c r="M95">
-        <v>113.0654103</v>
+        <v>114.2811674</v>
       </c>
       <c r="N95">
-        <v>175.8445897</v>
+        <v>174.6288326</v>
       </c>
       <c r="O95">
-        <v>52.75337691</v>
+        <v>52.38864978</v>
       </c>
       <c r="P95">
-        <v>123.09121279</v>
+        <v>122.24018282</v>
       </c>
       <c r="Q95">
-        <v>126.68121279</v>
+        <v>125.83018282</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7159029992311106</v>
+        <v>0.8243339052555624</v>
       </c>
       <c r="T95">
-        <v>5.739957366116913</v>
+        <v>6.668753056427096</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.555246553596064</v>
+        <v>2.528063079621639</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0967702343153337</v>
+        <v>0.09662035868448969</v>
       </c>
       <c r="C96">
-        <v>344.7275755273536</v>
+        <v>330.7496777341594</v>
       </c>
       <c r="D96">
-        <v>1846.973575527354</v>
+        <v>1849.90467773416</v>
       </c>
       <c r="E96">
-        <v>1556.246</v>
+        <v>1573.155</v>
       </c>
       <c r="F96">
-        <v>1589.446</v>
+        <v>1606.355</v>
       </c>
       <c r="G96">
         <v>87.2</v>
@@ -9159,28 +9159,28 @@
         <v>288.91</v>
       </c>
       <c r="M96">
-        <v>114.2811674</v>
+        <v>115.4969245</v>
       </c>
       <c r="N96">
-        <v>174.6288326</v>
+        <v>173.4130755</v>
       </c>
       <c r="O96">
-        <v>52.38864978</v>
+        <v>52.02392265</v>
       </c>
       <c r="P96">
-        <v>122.24018282</v>
+        <v>121.38915285</v>
       </c>
       <c r="Q96">
-        <v>125.83018282</v>
+        <v>124.97915285</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8243339052555624</v>
+        <v>0.976137173689795</v>
       </c>
       <c r="T96">
-        <v>6.668753056427096</v>
+        <v>7.969067022861351</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.528063079621639</v>
+        <v>2.501451889309831</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09662035868448969</v>
+        <v>0.09909128305364569</v>
       </c>
       <c r="C97">
-        <v>330.7496777341594</v>
+        <v>266.6744196240102</v>
       </c>
       <c r="D97">
-        <v>1849.90467773416</v>
+        <v>1802.73841962401</v>
       </c>
       <c r="E97">
-        <v>1573.155</v>
+        <v>1590.064</v>
       </c>
       <c r="F97">
-        <v>1606.355</v>
+        <v>1623.264</v>
       </c>
       <c r="G97">
         <v>87.2</v>
@@ -9241,45 +9241,45 @@
         <v>288.91</v>
       </c>
       <c r="M97">
-        <v>115.4969245</v>
+        <v>123.0434112</v>
       </c>
       <c r="N97">
-        <v>173.4130755</v>
+        <v>165.8665888</v>
       </c>
       <c r="O97">
-        <v>52.02392265</v>
+        <v>49.75997664</v>
       </c>
       <c r="P97">
-        <v>121.38915285</v>
+        <v>116.10661216</v>
       </c>
       <c r="Q97">
-        <v>124.97915285</v>
+        <v>119.69661216</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.976137173689795</v>
+        <v>1.203842076341144</v>
       </c>
       <c r="T97">
-        <v>7.969067022861351</v>
+        <v>9.919537972512737</v>
       </c>
       <c r="U97">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V97">
         <v>0.3</v>
       </c>
       <c r="W97">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.501451889309831</v>
+        <v>2.348033081839655</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09909128305364569</v>
+        <v>0.09896870742280167</v>
       </c>
       <c r="C98">
-        <v>266.6744196240102</v>
+        <v>252.0484364966155</v>
       </c>
       <c r="D98">
-        <v>1802.73841962401</v>
+        <v>1805.021436496615</v>
       </c>
       <c r="E98">
-        <v>1590.064</v>
+        <v>1606.973</v>
       </c>
       <c r="F98">
-        <v>1623.264</v>
+        <v>1640.173</v>
       </c>
       <c r="G98">
         <v>87.2</v>
@@ -9323,28 +9323,28 @@
         <v>288.91</v>
       </c>
       <c r="M98">
-        <v>123.0434112</v>
+        <v>124.3251134</v>
       </c>
       <c r="N98">
-        <v>165.8665888</v>
+        <v>164.5848866</v>
       </c>
       <c r="O98">
-        <v>49.75997664</v>
+        <v>49.37546598</v>
       </c>
       <c r="P98">
-        <v>116.10661216</v>
+        <v>115.20942062</v>
       </c>
       <c r="Q98">
-        <v>119.69661216</v>
+        <v>118.79942062</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.203842076341141</v>
+        <v>1.583350247426721</v>
       </c>
       <c r="T98">
-        <v>9.919537972512709</v>
+        <v>13.17032288859834</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.348033081839655</v>
+        <v>2.323826555222752</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09896870742280167</v>
+        <v>0.09884613179195766</v>
       </c>
       <c r="C99">
-        <v>252.0484364966155</v>
+        <v>237.4282431999848</v>
       </c>
       <c r="D99">
-        <v>1805.021436496615</v>
+        <v>1807.310243199985</v>
       </c>
       <c r="E99">
-        <v>1606.973</v>
+        <v>1623.882</v>
       </c>
       <c r="F99">
-        <v>1640.173</v>
+        <v>1657.082</v>
       </c>
       <c r="G99">
         <v>87.2</v>
@@ -9405,28 +9405,28 @@
         <v>288.91</v>
       </c>
       <c r="M99">
-        <v>124.3251134</v>
+        <v>125.6068156</v>
       </c>
       <c r="N99">
-        <v>164.5848866</v>
+        <v>163.3031844</v>
       </c>
       <c r="O99">
-        <v>49.37546598</v>
+        <v>48.99095532</v>
       </c>
       <c r="P99">
-        <v>115.20942062</v>
+        <v>114.31222908</v>
       </c>
       <c r="Q99">
-        <v>118.79942062</v>
+        <v>117.90222908</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.583350247426721</v>
+        <v>2.34236658959788</v>
       </c>
       <c r="T99">
-        <v>13.17032288859834</v>
+        <v>19.67189272076959</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.323826555222752</v>
+        <v>2.300114039353132</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09884613179195766</v>
+        <v>0.09872355616111364</v>
       </c>
       <c r="C100">
-        <v>237.4282431999848</v>
+        <v>222.8138617869793</v>
       </c>
       <c r="D100">
-        <v>1807.310243199985</v>
+        <v>1809.604861786979</v>
       </c>
       <c r="E100">
-        <v>1623.882</v>
+        <v>1640.791</v>
       </c>
       <c r="F100">
-        <v>1657.082</v>
+        <v>1673.991</v>
       </c>
       <c r="G100">
         <v>87.2</v>
@@ -9487,28 +9487,28 @@
         <v>288.91</v>
       </c>
       <c r="M100">
-        <v>125.6068156</v>
+        <v>126.8885178</v>
       </c>
       <c r="N100">
-        <v>163.3031844</v>
+        <v>162.0214822</v>
       </c>
       <c r="O100">
-        <v>48.99095532</v>
+        <v>48.60644466000001</v>
       </c>
       <c r="P100">
-        <v>114.31222908</v>
+        <v>113.41503754</v>
       </c>
       <c r="Q100">
-        <v>117.90222908</v>
+        <v>117.00503754</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.34236658959788</v>
+        <v>4.61941561611136</v>
       </c>
       <c r="T100">
-        <v>19.67189272076959</v>
+        <v>39.17660221728335</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.300114039353132</v>
+        <v>2.276880564208151</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09872355616111364</v>
-      </c>
-      <c r="C101">
-        <v>222.8138617869793</v>
-      </c>
-      <c r="D101">
-        <v>1809.604861786979</v>
-      </c>
-      <c r="E101">
-        <v>1640.791</v>
-      </c>
-      <c r="F101">
-        <v>1673.991</v>
-      </c>
-      <c r="G101">
-        <v>87.2</v>
-      </c>
-      <c r="H101">
-        <v>1657.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>292.5</v>
-      </c>
-      <c r="K101">
-        <v>3.59</v>
-      </c>
-      <c r="L101">
-        <v>288.91</v>
-      </c>
-      <c r="M101">
-        <v>126.8885178</v>
-      </c>
-      <c r="N101">
-        <v>162.0214822</v>
-      </c>
-      <c r="O101">
-        <v>48.60644466000001</v>
-      </c>
-      <c r="P101">
-        <v>113.41503754</v>
-      </c>
-      <c r="Q101">
-        <v>117.00503754</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.61941561611136</v>
-      </c>
-      <c r="T101">
-        <v>39.17660221728335</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.276880564208151</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
